--- a/2026_project/data_dictionary_Rev01.xlsx
+++ b/2026_project/data_dictionary_Rev01.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8708B564-9A55-44A2-85D6-68BF5F783A16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF48505B-0BCB-4878-B98E-FC4E4A4272BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="folder_overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="411">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1304" uniqueCount="496">
   <si>
     <t>value</t>
   </si>
@@ -1141,9 +1141,6 @@
     <t>Create distace matrix from pipeline_network, ship_routes</t>
   </si>
   <si>
-    <t>iii_manual_update</t>
-  </si>
-  <si>
     <t>combined_selected_manual_edit, pipeline_network_manual_edit, ship_routes_manual_edit</t>
   </si>
   <si>
@@ -1170,14 +1167,6 @@
     <t>connection.csv</t>
   </si>
   <si>
-    <t>ii_data_processing
-(preparing files in 2_data_processed)</t>
-  </si>
-  <si>
-    <t>i_etl_raw_to_db
-(import files from 1_raw)</t>
-  </si>
-  <si>
     <t>assign_technologies_to_nodes()</t>
   </si>
   <si>
@@ -1220,9 +1209,6 @@
     <t>optimization_results.h5</t>
   </si>
   <si>
-    <t>result.py</t>
-  </si>
-  <si>
     <t>2026_project\3_model_inputs</t>
   </si>
   <si>
@@ -1241,10 +1227,6 @@
     <t>Reading optimization_results.h5 and summmarise  into an excel file</t>
   </si>
   <si>
-    <t>main.py
-(configure parameter and scenario selection if any)</t>
-  </si>
-  <si>
     <t>From adopt_net0</t>
   </si>
   <si>
@@ -1254,12 +1236,6 @@
     <t>optimization_results.h5 &amp; scenario_state.json</t>
   </si>
   <si>
-    <t>Execute main.py by step up reduction target</t>
-  </si>
-  <si>
-    <t>Execute result.py for each reduction target</t>
-  </si>
-  <si>
     <t>loop_model.py</t>
   </si>
   <si>
@@ -1297,9 +1273,6 @@
   </si>
   <si>
     <t>Manual</t>
-  </si>
-  <si>
-    <t>Calculated</t>
   </si>
   <si>
     <t>Convert from their original projection into WGS84</t>
@@ -1369,13 +1342,429 @@
   <si>
     <t>Parameter setting
 (Only important)</t>
+  </si>
+  <si>
+    <t>results.py</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Execute </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>results.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for each reduction target</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Execute </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>main.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> by step up reduction target</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>main.py</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(intitialize &amp; prepare files: 3_model_inputs
+based on scenario-if any)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>iii_manual_update</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(updating files in 2_data_processed)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ii_data_processing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(preparing files in 2_data_processed)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>i_etl_raw_to_db</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+(import files from 1_raw to database.duckdb)</t>
+    </r>
+  </si>
+  <si>
+    <t>facility name</t>
+  </si>
+  <si>
+    <t>reporting year</t>
+  </si>
+  <si>
+    <t>geographical coordinate in WGS84</t>
+  </si>
+  <si>
+    <t>CO2 emission in tonne per year</t>
+  </si>
+  <si>
+    <t>original subsector code</t>
+  </si>
+  <si>
+    <t>country code in ISO2</t>
+  </si>
+  <si>
+    <t>standardised subsector name: cement, steel, waste</t>
+  </si>
+  <si>
+    <t>default: climate_trace</t>
+  </si>
+  <si>
+    <t>groupping geological prospects into one point at highest capacity</t>
+  </si>
+  <si>
+    <t>manual define for analysis, not use for model</t>
+  </si>
+  <si>
+    <t>orginal prospect name</t>
+  </si>
+  <si>
+    <t>geographical coordination system</t>
+  </si>
+  <si>
+    <t>geographical coordination system in EPSG code</t>
+  </si>
+  <si>
+    <t>ratio between remaining per total capacity</t>
+  </si>
+  <si>
+    <t>1st year of injection</t>
+  </si>
+  <si>
+    <t>1st injection rate in MtCO2 per year</t>
+  </si>
+  <si>
+    <t>CO2 total storage capacity (min or P10) in MtCO2</t>
+  </si>
+  <si>
+    <t>CO2 total storage capacity (mean or P50) in MtCO2</t>
+  </si>
+  <si>
+    <t>CO2 total storage capacity (max or P90) in MtCO2</t>
+  </si>
+  <si>
+    <t>remaining CO2 storage capacity (from Eygpt study report), still developing oil&amp;gas prospect, in MtCO2</t>
+  </si>
+  <si>
+    <t>available CO2 storage capacity (from Eygpt study report), still developing oil&amp;gas prospect, in MtCO2</t>
+  </si>
+  <si>
+    <t>2nd year of injection</t>
+  </si>
+  <si>
+    <t>2nd injection rate in MtCO2 per year</t>
+  </si>
+  <si>
+    <t>3rd year of injection</t>
+  </si>
+  <si>
+    <t>3rd injection rate in MtCO2 per year</t>
+  </si>
+  <si>
+    <t>4th year of injection</t>
+  </si>
+  <si>
+    <t>4th injection rate in MtCO2 per year</t>
+  </si>
+  <si>
+    <t>receiving terminal for annoused project</t>
+  </si>
+  <si>
+    <t>approximated reservoir depth in mTVD, likely top reservoir</t>
+  </si>
+  <si>
+    <t>approximated current min pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated  current mean pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated  current max pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated min pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated  mean pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated max pressure in bar</t>
+  </si>
+  <si>
+    <t>approximated min reseroivr thickness in metres</t>
+  </si>
+  <si>
+    <t>approximated max reseroivr thickness in metres</t>
+  </si>
+  <si>
+    <t>approximated mean reseroivr thickness in metres</t>
+  </si>
+  <si>
+    <t>approximated min seal thickness in metres</t>
+  </si>
+  <si>
+    <t>region of prospect</t>
+  </si>
+  <si>
+    <t>total CO2 storage capacity in tonne</t>
+  </si>
+  <si>
+    <t>node name (facility/storage site/port)</t>
+  </si>
+  <si>
+    <t>storage site name (combined prospects)</t>
+  </si>
+  <si>
+    <t>combined total CO2 storage capacity in tonne</t>
+  </si>
+  <si>
+    <t>subsector name</t>
+  </si>
+  <si>
+    <t>data source</t>
+  </si>
+  <si>
+    <t>default: storage</t>
+  </si>
+  <si>
+    <t>node type (emitter/storage/port)</t>
+  </si>
+  <si>
+    <t>port screening for large industrial port)</t>
+  </si>
+  <si>
+    <t>sanitized node name (for naming folder)</t>
+  </si>
+  <si>
+    <t>CO2 emission in tonne per hour</t>
+  </si>
+  <si>
+    <t>comparison with Xiao's thesis</t>
+  </si>
+  <si>
+    <t>original pollution code, this study used CO2</t>
+  </si>
+  <si>
+    <t>original facility ID</t>
+  </si>
+  <si>
+    <t>company name</t>
+  </si>
+  <si>
+    <t>NUTS region source code</t>
+  </si>
+  <si>
+    <t>NUTS region source name</t>
+  </si>
+  <si>
+    <t>city name</t>
+  </si>
+  <si>
+    <t>original activity code, used for convert into subsector</t>
+  </si>
+  <si>
+    <t>original activity full name</t>
+  </si>
+  <si>
+    <t>CO2 emission in kg</t>
+  </si>
+  <si>
+    <t>default: eea</t>
+  </si>
+  <si>
+    <t>original method code</t>
+  </si>
+  <si>
+    <t>original method full name</t>
+  </si>
+  <si>
+    <t>average electricity price per country among high voltage user in EUR per Mwhe</t>
+  </si>
+  <si>
+    <t>default: emitter</t>
+  </si>
+  <si>
+    <t>average gas price per country convert from avg_price_EUR/MWhe into EUR/MWhth by COP = 2.67</t>
+  </si>
+  <si>
+    <t>emitter_to_emitter/port/terminal/alternative, terminal_to_storage</t>
+  </si>
+  <si>
+    <t>starting node</t>
+  </si>
+  <si>
+    <t>geographical coordinate in WGS84 of starting node</t>
+  </si>
+  <si>
+    <t>destination node</t>
+  </si>
+  <si>
+    <t>geographical coordinate in WGS84 of destination node</t>
+  </si>
+  <si>
+    <t>pipeline length in km</t>
+  </si>
+  <si>
+    <t>Calculated/Processed/Automated</t>
+  </si>
+  <si>
+    <t>port type screening</t>
+  </si>
+  <si>
+    <t>Boolean for port selection</t>
+  </si>
+  <si>
+    <t>port name</t>
+  </si>
+  <si>
+    <t>selected port name</t>
+  </si>
+  <si>
+    <t>port screening type</t>
+  </si>
+  <si>
+    <t>default: port</t>
+  </si>
+  <si>
+    <t>route ID</t>
+  </si>
+  <si>
+    <t>starting port</t>
+  </si>
+  <si>
+    <t>starting country code in ISO2</t>
+  </si>
+  <si>
+    <t>destination port</t>
+  </si>
+  <si>
+    <t>destination country code in ISO2</t>
+  </si>
+  <si>
+    <t>shipping route distance in km</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1466,6 +1855,23 @@
     <font>
       <sz val="11"/>
       <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1613,7 +2019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1621,13 +2027,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1665,29 +2070,22 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1696,7 +2094,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1708,9 +2106,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1720,20 +2115,8 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1743,9 +2126,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1762,24 +2142,73 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2090,207 +2519,181 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="48.36328125" style="15" customWidth="1"/>
-    <col min="2" max="2" width="34.6328125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="48.36328125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="34.6328125" style="6" customWidth="1"/>
     <col min="3" max="3" width="185.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="12" t="s">
         <v>264</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="57" t="s">
         <v>268</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>282</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="9" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="14"/>
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="57"/>
+      <c r="B3" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="14"/>
-      <c r="B4" s="9" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="57"/>
+      <c r="B4" s="8" t="s">
         <v>289</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="9" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="14"/>
-      <c r="B5" s="9" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="57"/>
+      <c r="B5" s="8" t="s">
         <v>290</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="9" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="14"/>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="57"/>
+      <c r="B6" s="8" t="s">
         <v>296</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="9" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="14"/>
-      <c r="B7" s="9" t="s">
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="57"/>
+      <c r="B7" s="8" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="9" t="s">
         <v>287</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="14"/>
-      <c r="B8" s="9" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="57"/>
+      <c r="B8" s="8" t="s">
         <v>293</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="9" t="s">
         <v>288</v>
       </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="14"/>
-      <c r="B9" s="9" t="s">
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="57"/>
+      <c r="B9" s="8" t="s">
         <v>294</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="9" t="s">
         <v>297</v>
       </c>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="14"/>
-      <c r="B10" s="9" t="s">
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" s="57"/>
+      <c r="B10" s="8" t="s">
         <v>295</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="9" t="s">
         <v>298</v>
       </c>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="50" t="s">
-        <v>365</v>
-      </c>
-      <c r="B11" s="9"/>
-      <c r="C11" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="14" t="s">
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="13" t="s">
+        <v>361</v>
+      </c>
+      <c r="B11" s="8"/>
+      <c r="C11" s="9" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="57" t="s">
         <v>269</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>299</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="9" t="s">
         <v>305</v>
       </c>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="14"/>
-      <c r="B13" s="9" t="s">
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="57"/>
+      <c r="B13" s="8" t="s">
         <v>300</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="9" t="s">
         <v>306</v>
       </c>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="14"/>
-      <c r="B14" s="9" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" s="57"/>
+      <c r="B14" s="8" t="s">
         <v>301</v>
       </c>
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="9" t="s">
         <v>307</v>
       </c>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="14"/>
-      <c r="B15" s="17" t="s">
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="57"/>
+      <c r="B15" s="16" t="s">
         <v>302</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="14"/>
-      <c r="B16" s="17" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="57"/>
+      <c r="B16" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="C16" s="18" t="s">
-        <v>339</v>
+      <c r="C16" s="17" t="s">
+        <v>338</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="14"/>
-      <c r="B17" s="17" t="s">
+      <c r="A17" s="57"/>
+      <c r="B17" s="16" t="s">
         <v>304</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>309</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="49" t="s">
-        <v>363</v>
-      </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="10" t="s">
-        <v>364</v>
+      <c r="A18" s="40" t="s">
+        <v>359</v>
+      </c>
+      <c r="B18" s="8"/>
+      <c r="C18" s="9" t="s">
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -2308,629 +2711,623 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="47.36328125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="28.54296875" customWidth="1"/>
+    <col min="2" max="2" width="41.81640625" customWidth="1"/>
     <col min="3" max="3" width="4.08984375" customWidth="1"/>
     <col min="4" max="4" width="79.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.5">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="33" t="s">
+      <c r="C1" s="29" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="19"/>
+      <c r="C2" s="18"/>
       <c r="D2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C3" s="30"/>
-      <c r="D3" s="29" t="s">
+      <c r="C3" s="26"/>
+      <c r="D3" t="s">
         <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C4" s="24"/>
-      <c r="D4" s="29" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
+      <c r="C4" s="23"/>
+      <c r="D4" t="s">
+        <v>373</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+      <c r="A7" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="B7" s="30" t="s">
         <v>313</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="21" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="20" t="s">
         <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="8" t="s">
+      <c r="A9" s="7" t="s">
         <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="7" t="s">
         <v>271</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="22" t="s">
         <v>272</v>
       </c>
-      <c r="B12" s="42" t="s">
-        <v>347</v>
-      </c>
-      <c r="C12" s="25"/>
+      <c r="B12" s="58" t="s">
+        <v>409</v>
+      </c>
+      <c r="C12" s="7"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="24" t="s">
         <v>310</v>
       </c>
-      <c r="B13" s="43"/>
-      <c r="C13" s="25"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="7"/>
       <c r="D13" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+      <c r="A14" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B14" s="43"/>
-      <c r="C14" s="25"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="7"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="28" t="s">
+      <c r="A15" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B15" s="43"/>
-      <c r="C15" s="25"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="7"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="B16" s="43"/>
-      <c r="C16" s="25"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="7"/>
       <c r="D16" t="s">
         <v>320</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="31" t="s">
+      <c r="A17" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="B17" s="43"/>
-      <c r="C17" s="25"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="7"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="28" t="s">
+      <c r="A18" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B18" s="43"/>
-      <c r="C18" s="25"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="7"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="28" t="s">
+      <c r="A19" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B19" s="43"/>
-      <c r="C19" s="25"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="7"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="25" t="s">
         <v>315</v>
       </c>
-      <c r="B20" s="43"/>
-      <c r="C20" s="25"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="7"/>
       <c r="D20" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="28" t="s">
+      <c r="A21" s="25" t="s">
         <v>312</v>
       </c>
-      <c r="B21" s="43"/>
-      <c r="C21" s="25"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="28" t="s">
+      <c r="A22" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B22" s="43"/>
-      <c r="C22" s="25"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="7"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B23" s="43"/>
-      <c r="C23" s="25"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="7"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="27" t="s">
+      <c r="A24" s="24" t="s">
         <v>274</v>
       </c>
-      <c r="B24" s="43"/>
-      <c r="C24" s="25"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="7"/>
       <c r="D24" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="7"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="25" t="s">
         <v>276</v>
       </c>
-      <c r="B26" s="43"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="7"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="25"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="7"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="43"/>
-      <c r="C28" s="25"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="7"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="25" t="s">
         <v>271</v>
       </c>
-      <c r="B29" s="43"/>
+      <c r="B29" s="59"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="28" t="s">
+      <c r="A30" s="25" t="s">
         <v>277</v>
       </c>
-      <c r="B30" s="43"/>
+      <c r="B30" s="59"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="28" t="s">
+      <c r="A31" s="25" t="s">
         <v>278</v>
       </c>
-      <c r="B31" s="43"/>
+      <c r="B31" s="59"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="24" t="s">
         <v>321</v>
       </c>
-      <c r="B32" s="43"/>
+      <c r="B32" s="59"/>
       <c r="D32" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="28" t="s">
+      <c r="A33" s="25" t="s">
         <v>279</v>
       </c>
-      <c r="B33" s="43"/>
+      <c r="B33" s="59"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="28" t="s">
+      <c r="A34" s="25" t="s">
         <v>280</v>
       </c>
-      <c r="B34" s="43"/>
+      <c r="B34" s="59"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="28" t="s">
+      <c r="A35" s="25" t="s">
         <v>314</v>
       </c>
-      <c r="B35" s="43"/>
+      <c r="B35" s="59"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="28" t="s">
+      <c r="A36" s="62" t="s">
         <v>273</v>
       </c>
-      <c r="B36" s="43"/>
+      <c r="B36" s="59"/>
     </row>
     <row r="37" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="31" t="s">
+      <c r="A37" s="27" t="s">
         <v>322</v>
       </c>
-      <c r="B37" s="43"/>
+      <c r="B37" s="59"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="23" t="s">
+      <c r="A38" s="22" t="s">
         <v>281</v>
       </c>
-      <c r="B38" s="42" t="s">
-        <v>346</v>
+      <c r="B38" s="58" t="s">
+        <v>408</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="27" t="s">
+      <c r="A39" s="24" t="s">
         <v>275</v>
       </c>
-      <c r="B39" s="45"/>
+      <c r="B39" s="61"/>
       <c r="D39" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B40" s="45"/>
+      <c r="B40" s="61"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="28" t="s">
+      <c r="A41" s="25" t="s">
         <v>334</v>
       </c>
-      <c r="B41" s="45"/>
+      <c r="B41" s="61"/>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="35" t="s">
+      <c r="A42" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="B42" s="45"/>
+      <c r="B42" s="61"/>
       <c r="D42" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B43" s="45"/>
+      <c r="B43" s="61"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="36" t="s">
+      <c r="A44" s="32" t="s">
         <v>335</v>
       </c>
-      <c r="B44" s="45"/>
+      <c r="B44" s="61"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="B45" s="45"/>
+      <c r="A45" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="B45" s="61"/>
       <c r="D45" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B46" s="45"/>
+      <c r="B46" s="61"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="27" t="s">
+      <c r="A47" s="24" t="s">
         <v>327</v>
       </c>
-      <c r="B47" s="45"/>
+      <c r="B47" s="61"/>
       <c r="D47" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="28" t="s">
+      <c r="A48" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B48" s="45"/>
+      <c r="B48" s="61"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="25" t="s">
         <v>332</v>
       </c>
-      <c r="B49" s="45"/>
+      <c r="B49" s="61"/>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="35" t="s">
+      <c r="A50" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="B50" s="45"/>
+      <c r="B50" s="61"/>
       <c r="D50" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="28" t="s">
+      <c r="A51" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B51" s="66"/>
+      <c r="B51" s="37"/>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="28" t="s">
-        <v>409</v>
-      </c>
-      <c r="B52" s="66"/>
+      <c r="A52" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B52" s="37"/>
     </row>
     <row r="53" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A53" s="67" t="s">
+      <c r="A53" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="B53" s="53"/>
+      <c r="D53" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A54" s="7"/>
+    </row>
+    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A55" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A56" s="34" t="s">
+        <v>337</v>
+      </c>
+      <c r="B56" s="58" t="s">
         <v>407</v>
       </c>
-      <c r="B53" s="68"/>
-      <c r="D53" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="8"/>
-    </row>
-    <row r="55" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A55" s="53" t="s">
+      <c r="D56" s="33" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A57" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B57" s="59"/>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A58" s="35" t="s">
+        <v>339</v>
+      </c>
+      <c r="B58" s="59"/>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A59" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B59" s="59"/>
+    </row>
+    <row r="60" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="A60" s="36" t="s">
         <v>342</v>
       </c>
-    </row>
-    <row r="56" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A56" s="39" t="s">
-        <v>338</v>
-      </c>
-      <c r="B56" s="46" t="s">
-        <v>337</v>
-      </c>
-      <c r="D56" s="37" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="28" t="s">
+      <c r="B60" s="59"/>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A61" s="31" t="s">
+        <v>330</v>
+      </c>
+      <c r="B61" s="59"/>
+      <c r="D61" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A62" s="31" t="s">
+        <v>344</v>
+      </c>
+      <c r="B62" s="59"/>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A63" s="31" t="s">
+        <v>333</v>
+      </c>
+      <c r="B63" s="59"/>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A64" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B57" s="43"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="40" t="s">
-        <v>340</v>
-      </c>
-      <c r="B58" s="43"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B59" s="43"/>
-    </row>
-    <row r="60" spans="1:4" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A60" s="41" t="s">
-        <v>343</v>
-      </c>
-      <c r="B60" s="43"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="35" t="s">
-        <v>330</v>
-      </c>
-      <c r="B61" s="43"/>
-      <c r="D61" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="35" t="s">
-        <v>345</v>
-      </c>
-      <c r="B62" s="43"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="35" t="s">
-        <v>333</v>
-      </c>
-      <c r="B63" s="43"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B64" s="66"/>
+      <c r="B64" s="37"/>
     </row>
     <row r="65" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A65" s="67" t="s">
-        <v>407</v>
-      </c>
-      <c r="B65" s="68"/>
+      <c r="A65" s="52" t="s">
+        <v>399</v>
+      </c>
+      <c r="B65" s="53"/>
       <c r="D65" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="47" t="s">
+      <c r="A67" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="B67" s="58" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A68" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B68" s="59"/>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A69" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="B69" s="59"/>
+      <c r="D69" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="B67" s="42" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="28" t="s">
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A70" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B68" s="43"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="36" t="s">
-        <v>351</v>
-      </c>
-      <c r="B69" s="43"/>
-      <c r="D69" s="7" t="s">
+      <c r="B70" s="59"/>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A71" s="35" t="s">
+        <v>349</v>
+      </c>
+      <c r="B71" s="59"/>
+      <c r="D71" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A72" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B72" s="59"/>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A73" s="35" t="s">
+        <v>345</v>
+      </c>
+      <c r="B73" s="59"/>
+      <c r="D73" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A74" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B74" s="59"/>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A75" s="32" t="s">
+        <v>350</v>
+      </c>
+      <c r="B75" s="59"/>
+      <c r="D75" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A76" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B76" s="59"/>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A77" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="B77" s="59"/>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A78" s="32" t="s">
+        <v>347</v>
+      </c>
+      <c r="B78" s="59"/>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A79" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B79" s="59"/>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A80" s="31" t="s">
+        <v>358</v>
+      </c>
+      <c r="B80" s="59"/>
+      <c r="D80" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A81" s="41" t="s">
+        <v>215</v>
+      </c>
+      <c r="B81" s="60"/>
+      <c r="D81" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A83" s="43" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A84" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="B84" s="63" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A85" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="B85" s="59"/>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A86" s="42" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B70" s="43"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="40" t="s">
-        <v>352</v>
-      </c>
-      <c r="B71" s="43"/>
-      <c r="D71" t="s">
+      <c r="B86" s="59"/>
+      <c r="D86" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A87" s="41" t="s">
         <v>356</v>
       </c>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B72" s="43"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="40" t="s">
-        <v>348</v>
-      </c>
-      <c r="B73" s="43"/>
-      <c r="D73" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B74" s="43"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="36" t="s">
-        <v>353</v>
-      </c>
-      <c r="B75" s="43"/>
-      <c r="D75" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B76" s="43"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="36" t="s">
-        <v>349</v>
-      </c>
-      <c r="B77" s="43"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="36" t="s">
-        <v>350</v>
-      </c>
-      <c r="B78" s="43"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B79" s="43"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="B80" s="43"/>
-      <c r="D80" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A81" s="51" t="s">
-        <v>215</v>
-      </c>
-      <c r="B81" s="44"/>
-      <c r="D81" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A83" s="53" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="26" t="s">
-        <v>372</v>
-      </c>
-      <c r="B84" s="46" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="28" t="s">
-        <v>281</v>
-      </c>
-      <c r="B85" s="43"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="52" t="s">
-        <v>360</v>
-      </c>
-      <c r="B86" s="43"/>
-      <c r="D86" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A87" s="51" t="s">
-        <v>359</v>
-      </c>
-      <c r="B87" s="44"/>
+      <c r="B87" s="60"/>
       <c r="D87" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="47" t="s">
-        <v>373</v>
-      </c>
-      <c r="B89" s="46" t="s">
-        <v>375</v>
+      <c r="A89" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="B89" s="63" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="28" t="s">
+      <c r="A90" s="25" t="s">
         <v>281</v>
       </c>
-      <c r="B90" s="43"/>
+      <c r="B90" s="59"/>
       <c r="D90" t="s">
-        <v>376</v>
+        <v>369</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A91" s="48" t="s">
-        <v>374</v>
-      </c>
-      <c r="B91" s="44"/>
+      <c r="A91" s="39" t="s">
+        <v>404</v>
+      </c>
+      <c r="B91" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2953,197 +3350,215 @@
     <col min="1" max="1" width="29.6328125" customWidth="1"/>
     <col min="2" max="2" width="36.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.81640625" customWidth="1"/>
-    <col min="4" max="4" width="9.90625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="44.7265625" customWidth="1"/>
+    <col min="4" max="4" width="9.90625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="103.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="16" t="s">
-        <v>384</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>383</v>
-      </c>
-      <c r="C1" s="16" t="s">
+      <c r="A1" s="15" t="s">
+        <v>377</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>375</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="44" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="69">
+        <v>15580</v>
+      </c>
+      <c r="E2" s="44" t="s">
+        <v>410</v>
+      </c>
+      <c r="H2" s="46" t="s">
+        <v>379</v>
+      </c>
+      <c r="I2" t="s">
         <v>382</v>
       </c>
-      <c r="D1" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="E1" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="H1" s="20" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="54" t="s">
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A3" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="54" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="54">
+      <c r="B3" s="44" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="44" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="69">
         <v>15580</v>
       </c>
-      <c r="E2" s="54"/>
-      <c r="H2" s="56" t="s">
-        <v>386</v>
-      </c>
-      <c r="I2" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="54" t="s">
+      <c r="E3" s="44" t="s">
+        <v>411</v>
+      </c>
+      <c r="H3" s="45" t="s">
+        <v>379</v>
+      </c>
+      <c r="I3" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A4" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="54" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="54" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3" s="54">
+      <c r="B4" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="69">
         <v>15580</v>
       </c>
-      <c r="E3" s="54"/>
-      <c r="H3" s="55" t="s">
-        <v>386</v>
-      </c>
-      <c r="I3" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="54" t="s">
+      <c r="E4" s="44" t="s">
+        <v>412</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>379</v>
+      </c>
+      <c r="I4" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A5" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="54" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="54">
+      <c r="B5" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="69">
         <v>15580</v>
       </c>
-      <c r="E4" s="54"/>
-      <c r="H4" s="57" t="s">
-        <v>386</v>
-      </c>
-      <c r="I4" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="54" t="s">
+      <c r="E5" s="44" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A6" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="54">
+      <c r="B6" s="44" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="69">
         <v>15580</v>
       </c>
-      <c r="E5" s="54"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="54" t="s">
+      <c r="E6" s="44" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A7" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="54" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="54">
+      <c r="B7" s="44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D7" s="69">
         <v>15580</v>
       </c>
-      <c r="E6" s="54"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="54" t="s">
+      <c r="E7" s="44" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A8" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="54" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="54">
+      <c r="B8" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D8" s="69">
         <v>15580</v>
       </c>
-      <c r="E7" s="54"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="54" t="s">
+      <c r="E8" s="44" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="54" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D8" s="54">
+      <c r="B9" s="44" t="s">
+        <v>13</v>
+      </c>
+      <c r="C9" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D9" s="69">
         <v>15580</v>
       </c>
-      <c r="E8" s="54"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="54" t="s">
+      <c r="E9" s="44" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="54" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" s="54">
+      <c r="B10" s="44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D10" s="69">
         <v>15580</v>
       </c>
-      <c r="E9" s="54"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="54" t="s">
-        <v>2</v>
-      </c>
-      <c r="B10" s="54" t="s">
+      <c r="E10" s="44" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D10" s="54">
-        <v>15580</v>
-      </c>
-      <c r="E10" s="54"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D11" s="56">
+      <c r="C11" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D11" s="70">
         <v>221</v>
       </c>
-      <c r="E11" s="56"/>
+      <c r="E11" s="46"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
@@ -3155,112 +3570,129 @@
       <c r="C12" t="s">
         <v>4</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="6">
         <v>221</v>
       </c>
+      <c r="E12" s="64" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="56" t="s">
+      <c r="A13" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B13" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="56">
+      <c r="C13" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="70">
         <v>221</v>
       </c>
-      <c r="E13" s="56"/>
+      <c r="E13" s="46"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="47" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="47" t="s">
         <v>17</v>
       </c>
-      <c r="C14" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="55">
+      <c r="C14" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="72">
         <v>221</v>
       </c>
+      <c r="E14" s="47" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="56" t="s">
+      <c r="A15" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="56" t="s">
+      <c r="B15" s="46" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="56" t="s">
+      <c r="C15" s="46" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="56">
+      <c r="D15" s="70">
         <v>221</v>
       </c>
-      <c r="E15" s="56"/>
+      <c r="E15" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="C16" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16" s="56">
+      <c r="C16" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="70">
         <v>221</v>
       </c>
-      <c r="E16" s="56"/>
+      <c r="E16" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="C17" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="55">
+      <c r="C17" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D17" s="71">
         <v>221</v>
       </c>
+      <c r="E17" s="45" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="56" t="s">
+      <c r="A18" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="56" t="s">
+      <c r="B18" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="C18" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="56">
+      <c r="C18" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D18" s="70">
         <v>221</v>
       </c>
-      <c r="E18" s="56"/>
+      <c r="E18" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="56" t="s">
+      <c r="A19" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B19" s="56" t="s">
+      <c r="B19" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="56">
+      <c r="C19" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D19" s="70">
         <v>221</v>
       </c>
-      <c r="E19" s="56"/>
+      <c r="E19" s="46" t="s">
+        <v>419</v>
+      </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
@@ -3272,8 +3704,11 @@
       <c r="C20" t="s">
         <v>8</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="6">
         <v>221</v>
+      </c>
+      <c r="E20" s="64" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -3286,478 +3721,539 @@
       <c r="C21" t="s">
         <v>8</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="6">
         <v>221</v>
       </c>
+      <c r="E21" s="64" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="57" t="s">
+      <c r="A22" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="45" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="57">
+      <c r="C22" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="71">
         <v>221</v>
       </c>
-      <c r="E22" s="57" t="s">
-        <v>389</v>
+      <c r="E22" s="45" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="57" t="s">
+      <c r="A23" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C23" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="D23" s="57">
+      <c r="C23" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="71">
         <v>221</v>
       </c>
-      <c r="E23" s="57" t="s">
-        <v>389</v>
+      <c r="E23" s="45" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="55" t="s">
+      <c r="A24" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B24" s="55" t="s">
+      <c r="B24" s="45" t="s">
         <v>25</v>
       </c>
-      <c r="C24" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D24" s="55">
+      <c r="C24" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="71">
         <v>221</v>
       </c>
-      <c r="E24" s="55"/>
+      <c r="E24" s="45" t="s">
+        <v>421</v>
+      </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="55" t="s">
+      <c r="A25" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B25" s="55" t="s">
+      <c r="B25" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="C25" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="55">
+      <c r="C25" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="71">
         <v>221</v>
       </c>
-      <c r="E25" s="55"/>
+      <c r="E25" s="45" t="s">
+        <v>422</v>
+      </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="56" t="s">
+      <c r="A26" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="56" t="s">
+      <c r="B26" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="56">
+      <c r="C26" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D26" s="70">
         <v>221</v>
       </c>
-      <c r="E26" s="56"/>
+      <c r="E26" s="46" t="s">
+        <v>426</v>
+      </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="55" t="s">
+      <c r="A27" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="B27" s="55" t="s">
+      <c r="B27" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="C27" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="55">
+      <c r="C27" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D27" s="71">
         <v>221</v>
       </c>
-      <c r="E27" s="55"/>
+      <c r="E27" s="45" t="s">
+        <v>427</v>
+      </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="56" t="s">
+      <c r="A28" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B28" s="56" t="s">
+      <c r="B28" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="C28" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="56">
+      <c r="C28" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D28" s="70">
         <v>221</v>
       </c>
-      <c r="E28" s="56"/>
+      <c r="E28" s="46" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="56" t="s">
+      <c r="A29" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="56" t="s">
+      <c r="B29" s="46" t="s">
         <v>30</v>
       </c>
-      <c r="C29" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="56">
+      <c r="C29" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="70">
         <v>221</v>
       </c>
-      <c r="E29" s="56"/>
+      <c r="E29" s="46" t="s">
+        <v>429</v>
+      </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="56" t="s">
+      <c r="A30" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="56" t="s">
+      <c r="B30" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C30" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="56">
+      <c r="C30" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="70">
         <v>221</v>
       </c>
-      <c r="E30" s="56"/>
+      <c r="E30" s="46" t="s">
+        <v>430</v>
+      </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="56" t="s">
+      <c r="A31" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B31" s="56" t="s">
+      <c r="B31" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C31" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="56">
+      <c r="C31" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D31" s="70">
         <v>221</v>
       </c>
-      <c r="E31" s="56"/>
+      <c r="E31" s="46" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="56" t="s">
+      <c r="A32" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B32" s="56" t="s">
+      <c r="B32" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="C32" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="56">
+      <c r="C32" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" s="70">
         <v>221</v>
       </c>
-      <c r="E32" s="55"/>
+      <c r="E32" s="46" t="s">
+        <v>424</v>
+      </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="56" t="s">
+      <c r="A33" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="56" t="s">
+      <c r="B33" s="46" t="s">
         <v>34</v>
       </c>
-      <c r="C33" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="56">
+      <c r="C33" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="70">
         <v>221</v>
       </c>
-      <c r="E33" s="55"/>
+      <c r="E33" s="46" t="s">
+        <v>425</v>
+      </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="56" t="s">
+      <c r="A34" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B34" s="56" t="s">
+      <c r="B34" s="46" t="s">
         <v>35</v>
       </c>
-      <c r="C34" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="56">
+      <c r="C34" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="70">
         <v>221</v>
       </c>
-      <c r="E34" s="55"/>
+      <c r="E34" s="46" t="s">
+        <v>431</v>
+      </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="56" t="s">
+      <c r="A35" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B35" s="56" t="s">
+      <c r="B35" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D35" s="56">
+      <c r="C35" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="70">
         <v>221</v>
       </c>
-      <c r="E35" s="55"/>
+      <c r="E35" s="46" t="s">
+        <v>432</v>
+      </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="56" t="s">
+      <c r="A36" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B36" s="56" t="s">
+      <c r="B36" s="46" t="s">
         <v>37</v>
       </c>
-      <c r="C36" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="56">
+      <c r="C36" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D36" s="70">
         <v>221</v>
       </c>
-      <c r="E36" s="55"/>
+      <c r="E36" s="46" t="s">
+        <v>433</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="56" t="s">
+      <c r="A37" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="56" t="s">
+      <c r="B37" s="46" t="s">
         <v>38</v>
       </c>
-      <c r="C37" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D37" s="56">
+      <c r="C37" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D37" s="70">
         <v>221</v>
       </c>
-      <c r="E37" s="55"/>
+      <c r="E37" s="46" t="s">
+        <v>434</v>
+      </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="56" t="s">
+      <c r="A38" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C38" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D38" s="56">
+      <c r="C38" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="70">
         <v>221</v>
       </c>
-      <c r="E38" s="55"/>
+      <c r="E38" s="46" t="s">
+        <v>435</v>
+      </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A39" s="56" t="s">
+      <c r="A39" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B39" s="56" t="s">
+      <c r="B39" s="46" t="s">
         <v>40</v>
       </c>
-      <c r="C39" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="56">
+      <c r="C39" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D39" s="70">
         <v>221</v>
       </c>
-      <c r="E39" s="55"/>
+      <c r="E39" s="46" t="s">
+        <v>436</v>
+      </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="56" t="s">
+      <c r="A40" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="46" t="s">
         <v>41</v>
       </c>
-      <c r="C40" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D40" s="56">
+      <c r="C40" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D40" s="70">
         <v>221</v>
       </c>
-      <c r="E40" s="56"/>
+      <c r="E40" s="46" t="s">
+        <v>437</v>
+      </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="56" t="s">
+      <c r="A41" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B41" s="56" t="s">
+      <c r="B41" s="46" t="s">
         <v>42</v>
       </c>
-      <c r="C41" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="56">
+      <c r="C41" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="70">
         <v>221</v>
       </c>
-      <c r="E41" s="56"/>
+      <c r="E41" s="46" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="56" t="s">
+      <c r="A42" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B42" s="56" t="s">
+      <c r="B42" s="46" t="s">
         <v>43</v>
       </c>
-      <c r="C42" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="56">
+      <c r="C42" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D42" s="70">
         <v>221</v>
       </c>
-      <c r="E42" s="56"/>
+      <c r="E42" s="46" t="s">
+        <v>440</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="56" t="s">
+      <c r="A43" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="56" t="s">
+      <c r="B43" s="46" t="s">
         <v>44</v>
       </c>
-      <c r="C43" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="56">
+      <c r="C43" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D43" s="70">
         <v>221</v>
       </c>
-      <c r="E43" s="56"/>
+      <c r="E43" s="46" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="56" t="s">
+      <c r="A44" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B44" s="56" t="s">
+      <c r="B44" s="46" t="s">
         <v>45</v>
       </c>
-      <c r="C44" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="56">
+      <c r="C44" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="70">
         <v>221</v>
       </c>
-      <c r="E44" s="56"/>
+      <c r="E44" s="46" t="s">
+        <v>442</v>
+      </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="56" t="s">
+      <c r="A45" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B45" s="56" t="s">
+      <c r="B45" s="46" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="56">
+      <c r="C45" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="70">
         <v>221</v>
       </c>
-      <c r="E45" s="56"/>
+      <c r="E45" s="46" t="s">
+        <v>443</v>
+      </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="56" t="s">
+      <c r="A46" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B46" s="56" t="s">
+      <c r="B46" s="46" t="s">
         <v>47</v>
       </c>
-      <c r="C46" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D46" s="56">
+      <c r="C46" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D46" s="70">
         <v>221</v>
       </c>
-      <c r="E46" s="56"/>
+      <c r="E46" s="46" t="s">
+        <v>444</v>
+      </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="56" t="s">
+      <c r="A47" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B47" s="56" t="s">
+      <c r="B47" s="46" t="s">
         <v>48</v>
       </c>
-      <c r="C47" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="56">
+      <c r="C47" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="70">
         <v>221</v>
       </c>
-      <c r="E47" s="56"/>
+      <c r="E47" s="46" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="56" t="s">
+      <c r="A48" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B48" s="56" t="s">
+      <c r="B48" s="46" t="s">
         <v>49</v>
       </c>
-      <c r="C48" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D48" s="56">
+      <c r="C48" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="70">
         <v>221</v>
       </c>
-      <c r="E48" s="56"/>
+      <c r="E48" s="46" t="s">
+        <v>445</v>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="56" t="s">
+      <c r="A49" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B49" s="56" t="s">
+      <c r="B49" s="46" t="s">
         <v>50</v>
       </c>
-      <c r="C49" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="56">
+      <c r="C49" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D49" s="70">
         <v>221</v>
       </c>
-      <c r="E49" s="56"/>
+      <c r="E49" s="46" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="56" t="s">
+      <c r="A50" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B50" s="56" t="s">
+      <c r="B50" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="C50" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="56">
+      <c r="C50" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D50" s="70">
         <v>221</v>
       </c>
-      <c r="E50" s="56"/>
+      <c r="E50" s="46" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="56" t="s">
+      <c r="A51" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B51" s="56" t="s">
+      <c r="B51" s="46" t="s">
         <v>52</v>
       </c>
-      <c r="C51" s="56" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="56">
+      <c r="C51" s="46" t="s">
+        <v>8</v>
+      </c>
+      <c r="D51" s="70">
         <v>221</v>
       </c>
-      <c r="E51" s="56"/>
+      <c r="E51" s="46" t="s">
+        <v>448</v>
+      </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="56" t="s">
+      <c r="A52" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="B52" s="56" t="s">
+      <c r="B52" s="46" t="s">
         <v>53</v>
       </c>
-      <c r="C52" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D52" s="56">
+      <c r="C52" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D52" s="70">
         <v>221</v>
       </c>
-      <c r="E52" s="56"/>
+      <c r="E52" s="46" t="s">
+        <v>449</v>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
@@ -3769,129 +4265,146 @@
       <c r="C53" t="s">
         <v>8</v>
       </c>
-      <c r="D53">
+      <c r="D53" s="6">
         <v>221</v>
       </c>
+      <c r="E53" s="65" t="s">
+        <v>450</v>
+      </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="54" t="s">
+      <c r="A54" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B54" s="54" t="s">
+      <c r="B54" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C54" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D54" s="54">
+      <c r="C54" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D54" s="69">
         <v>7</v>
       </c>
-      <c r="E54" s="54"/>
+      <c r="E54" s="44" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="54" t="s">
+      <c r="A55" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B55" s="54" t="s">
+      <c r="B55" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C55" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D55" s="54">
+      <c r="C55" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D55" s="69">
         <v>7</v>
       </c>
-      <c r="E55" s="54"/>
+      <c r="E55" s="44" t="s">
+        <v>452</v>
+      </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="54" t="s">
+      <c r="A56" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B56" s="54" t="s">
+      <c r="B56" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C56" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D56" s="54">
+      <c r="C56" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D56" s="69">
         <v>7</v>
       </c>
-      <c r="E56" s="54"/>
+      <c r="E56" s="44" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="54" t="s">
+      <c r="A57" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B57" s="54" t="s">
+      <c r="B57" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C57" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="54">
+      <c r="C57" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="69">
         <v>7</v>
       </c>
-      <c r="E57" s="54"/>
+      <c r="E57" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="54" t="s">
+      <c r="A58" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B58" s="54" t="s">
+      <c r="B58" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C58" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="54">
+      <c r="C58" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="69">
         <v>7</v>
       </c>
-      <c r="E58" s="54"/>
+      <c r="E58" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="54" t="s">
+      <c r="A59" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B59" s="54" t="s">
+      <c r="B59" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="C59" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="54">
+      <c r="C59" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="69">
         <v>7</v>
       </c>
-      <c r="E59" s="54"/>
+      <c r="E59" s="44" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="54" t="s">
+      <c r="A60" s="50" t="s">
         <v>55</v>
       </c>
-      <c r="B60" s="54" t="s">
+      <c r="B60" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C60" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D60" s="54">
+      <c r="C60" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D60" s="73">
         <v>7</v>
       </c>
-      <c r="E60" s="54"/>
+      <c r="E60" s="50" t="s">
+        <v>456</v>
+      </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="54" t="s">
+      <c r="A61" s="44" t="s">
         <v>55</v>
       </c>
-      <c r="B61" s="54" t="s">
+      <c r="B61" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C61" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D61" s="54">
+      <c r="C61" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D61" s="69">
         <v>7</v>
       </c>
-      <c r="E61" s="54"/>
+      <c r="E61" s="44"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
@@ -3903,8 +4416,11 @@
       <c r="C62" t="s">
         <v>4</v>
       </c>
-      <c r="D62">
+      <c r="D62" s="6">
         <v>144</v>
+      </c>
+      <c r="E62" s="64" t="s">
+        <v>418</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.35">
@@ -3917,8 +4433,11 @@
       <c r="C63" t="s">
         <v>4</v>
       </c>
-      <c r="D63">
+      <c r="D63" s="6">
         <v>144</v>
+      </c>
+      <c r="E63" s="64" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.35">
@@ -3931,8 +4450,11 @@
       <c r="C64" t="s">
         <v>4</v>
       </c>
-      <c r="D64">
+      <c r="D64" s="6">
         <v>144</v>
+      </c>
+      <c r="E64" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.35">
@@ -3945,8 +4467,11 @@
       <c r="C65" t="s">
         <v>8</v>
       </c>
-      <c r="D65">
+      <c r="D65" s="6">
         <v>144</v>
+      </c>
+      <c r="E65" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
@@ -3959,8 +4484,11 @@
       <c r="C66" t="s">
         <v>8</v>
       </c>
-      <c r="D66">
+      <c r="D66" s="6">
         <v>144</v>
+      </c>
+      <c r="E66" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.35">
@@ -3973,8 +4501,11 @@
       <c r="C67" t="s">
         <v>8</v>
       </c>
-      <c r="D67">
+      <c r="D67" s="6">
         <v>144</v>
+      </c>
+      <c r="E67" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -3987,8 +4518,11 @@
       <c r="C68" t="s">
         <v>8</v>
       </c>
-      <c r="D68">
+      <c r="D68" s="6">
         <v>144</v>
+      </c>
+      <c r="E68" t="s">
+        <v>453</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.35">
@@ -4001,8 +4535,11 @@
       <c r="C69" t="s">
         <v>4</v>
       </c>
-      <c r="D69">
+      <c r="D69" s="6">
         <v>144</v>
+      </c>
+      <c r="E69" t="s">
+        <v>454</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
@@ -4015,8 +4552,11 @@
       <c r="C70" t="s">
         <v>4</v>
       </c>
-      <c r="D70">
+      <c r="D70" s="6">
         <v>144</v>
+      </c>
+      <c r="E70" t="s">
+        <v>455</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
@@ -4029,8 +4569,11 @@
       <c r="C71" t="s">
         <v>4</v>
       </c>
-      <c r="D71">
+      <c r="D71" s="6">
         <v>144</v>
+      </c>
+      <c r="E71" t="s">
+        <v>457</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
@@ -4043,8 +4586,11 @@
       <c r="C72" t="s">
         <v>4</v>
       </c>
-      <c r="D72">
+      <c r="D72" s="6">
         <v>144</v>
+      </c>
+      <c r="E72" t="s">
+        <v>458</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
@@ -4057,327 +4603,368 @@
       <c r="C73" t="s">
         <v>19</v>
       </c>
-      <c r="D73">
+      <c r="D73" s="6">
         <v>144</v>
       </c>
+      <c r="E73" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" t="s">
+      <c r="A74" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B74" s="45" t="s">
         <v>58</v>
       </c>
-      <c r="C74" t="s">
-        <v>4</v>
-      </c>
-      <c r="D74">
+      <c r="C74" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D74" s="71">
         <v>144</v>
       </c>
+      <c r="E74" s="45" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" t="s">
+      <c r="A75" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B75" s="45" t="s">
         <v>59</v>
       </c>
-      <c r="C75" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75">
+      <c r="C75" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D75" s="71">
         <v>144</v>
       </c>
+      <c r="E75" s="45" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="56" t="s">
+      <c r="A76" s="46" t="s">
         <v>56</v>
       </c>
-      <c r="B76" s="56" t="s">
+      <c r="B76" s="46" t="s">
         <v>60</v>
       </c>
-      <c r="C76" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D76" s="56">
+      <c r="C76" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D76" s="70">
         <v>144</v>
       </c>
-      <c r="E76" s="56"/>
+      <c r="E76" s="46" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="54" t="s">
+      <c r="A77" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B77" s="54" t="s">
+      <c r="B77" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="C77" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D77" s="54">
+      <c r="C77" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D77" s="69">
         <v>144</v>
       </c>
-      <c r="E77" s="54"/>
+      <c r="E77" s="44" t="s">
+        <v>418</v>
+      </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A78" s="54" t="s">
+      <c r="A78" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B78" s="54" t="s">
+      <c r="B78" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C78" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D78" s="54">
+      <c r="C78" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D78" s="69">
         <v>144</v>
       </c>
-      <c r="E78" s="54"/>
+      <c r="E78" s="44" t="s">
+        <v>451</v>
+      </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A79" s="54" t="s">
+      <c r="A79" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B79" s="54" t="s">
+      <c r="B79" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C79" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D79" s="54">
+      <c r="C79" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D79" s="69">
         <v>144</v>
       </c>
-      <c r="E79" s="54"/>
+      <c r="E79" s="44" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A80" s="54" t="s">
+      <c r="A80" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B80" s="54" t="s">
+      <c r="B80" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C80" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="54">
+      <c r="C80" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="69">
         <v>144</v>
       </c>
-      <c r="E80" s="54"/>
+      <c r="E80" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A81" s="54" t="s">
+      <c r="A81" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B81" s="54" t="s">
+      <c r="B81" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C81" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D81" s="54">
+      <c r="C81" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D81" s="69">
         <v>144</v>
       </c>
-      <c r="E81" s="54"/>
+      <c r="E81" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="54" t="s">
+      <c r="A82" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B82" s="54" t="s">
+      <c r="B82" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C82" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D82" s="54">
+      <c r="C82" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D82" s="69">
         <v>144</v>
       </c>
-      <c r="E82" s="54"/>
+      <c r="E82" s="44" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A83" s="54" t="s">
+      <c r="A83" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B83" s="54" t="s">
+      <c r="B83" s="44" t="s">
         <v>54</v>
       </c>
-      <c r="C83" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="54">
+      <c r="C83" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D83" s="69">
         <v>144</v>
       </c>
-      <c r="E83" s="54"/>
+      <c r="E83" s="44" t="s">
+        <v>453</v>
+      </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="54" t="s">
+      <c r="A84" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B84" s="54" t="s">
+      <c r="B84" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C84" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D84" s="54">
+      <c r="C84" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D84" s="69">
         <v>144</v>
       </c>
-      <c r="E84" s="54"/>
+      <c r="E84" s="44" t="s">
+        <v>454</v>
+      </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="54" t="s">
+      <c r="A85" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B85" s="54" t="s">
+      <c r="B85" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C85" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D85" s="54">
+      <c r="C85" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D85" s="69">
         <v>144</v>
       </c>
-      <c r="E85" s="54"/>
+      <c r="E85" s="44" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="54" t="s">
+      <c r="A86" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B86" s="54" t="s">
+      <c r="B86" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C86" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D86" s="54">
+      <c r="C86" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D86" s="69">
         <v>144</v>
       </c>
-      <c r="E86" s="54"/>
+      <c r="E86" s="44" t="s">
+        <v>457</v>
+      </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="54" t="s">
+      <c r="A87" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B87" s="54" t="s">
+      <c r="B87" s="44" t="s">
         <v>57</v>
       </c>
-      <c r="C87" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D87" s="54">
+      <c r="C87" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D87" s="69">
         <v>144</v>
       </c>
-      <c r="E87" s="54"/>
+      <c r="E87" s="44" t="s">
+        <v>458</v>
+      </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="54" t="s">
+      <c r="A88" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B88" s="54" t="s">
+      <c r="B88" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C88" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D88" s="54">
+      <c r="C88" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D88" s="69">
         <v>144</v>
       </c>
-      <c r="E88" s="54"/>
+      <c r="E88" s="44" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="54" t="s">
+      <c r="A89" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="B89" s="54" t="s">
+      <c r="B89" s="49" t="s">
         <v>58</v>
       </c>
-      <c r="C89" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D89" s="54">
+      <c r="C89" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D89" s="74">
         <v>144</v>
       </c>
-      <c r="E89" s="54"/>
+      <c r="E89" s="49" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="54" t="s">
+      <c r="A90" s="49" t="s">
         <v>61</v>
       </c>
-      <c r="B90" s="54" t="s">
+      <c r="B90" s="49" t="s">
         <v>59</v>
       </c>
-      <c r="C90" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D90" s="54">
+      <c r="C90" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D90" s="74">
         <v>144</v>
       </c>
-      <c r="E90" s="54"/>
+      <c r="E90" s="49" t="s">
+        <v>460</v>
+      </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="58" t="s">
+      <c r="A91" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="B91" s="58" t="s">
+      <c r="B91" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="C91" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="D91" s="58">
+      <c r="C91" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="D91" s="75">
         <v>144</v>
       </c>
-      <c r="E91" s="58"/>
+      <c r="E91" s="48" t="s">
+        <v>461</v>
+      </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="59" t="s">
+      <c r="A92" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="B92" s="59" t="s">
+      <c r="B92" s="76" t="s">
         <v>62</v>
       </c>
-      <c r="C92" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D92" s="59">
+      <c r="C92" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D92" s="77">
         <v>144</v>
       </c>
-      <c r="E92" s="59" t="s">
-        <v>396</v>
+      <c r="E92" s="76" t="s">
+        <v>388</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="59" t="s">
+      <c r="A93" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="B93" s="59" t="s">
+      <c r="B93" s="76" t="s">
         <v>63</v>
       </c>
-      <c r="C93" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D93" s="59">
+      <c r="C93" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D93" s="77">
         <v>144</v>
       </c>
-      <c r="E93" s="59" t="s">
-        <v>393</v>
+      <c r="E93" s="76" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="59" t="s">
+      <c r="A94" s="76" t="s">
         <v>61</v>
       </c>
-      <c r="B94" s="59" t="s">
+      <c r="B94" s="76" t="s">
         <v>64</v>
       </c>
-      <c r="C94" s="59" t="s">
-        <v>8</v>
-      </c>
-      <c r="D94" s="59">
+      <c r="C94" s="76" t="s">
+        <v>8</v>
+      </c>
+      <c r="D94" s="77">
         <v>144</v>
       </c>
-      <c r="E94" s="59" t="s">
-        <v>394</v>
+      <c r="E94" s="76" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
@@ -4390,38 +4977,46 @@
       <c r="C95" t="s">
         <v>4</v>
       </c>
-      <c r="D95">
+      <c r="D95" s="6">
         <v>37653</v>
       </c>
+      <c r="E95" s="66" t="s">
+        <v>462</v>
+      </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" t="s">
+      <c r="A96" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B96" s="46" t="s">
         <v>67</v>
       </c>
-      <c r="C96" t="s">
-        <v>4</v>
-      </c>
-      <c r="D96">
+      <c r="C96" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D96" s="70">
         <v>37653</v>
       </c>
+      <c r="E96" s="68" t="s">
+        <v>463</v>
+      </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="56" t="s">
+      <c r="A97" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B97" s="56" t="s">
+      <c r="B97" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="C97" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D97" s="56">
+      <c r="C97" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D97" s="70">
         <v>37653</v>
       </c>
-      <c r="E97" s="56"/>
+      <c r="E97" s="68" t="s">
+        <v>464</v>
+      </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
@@ -4433,8 +5028,11 @@
       <c r="C98" t="s">
         <v>4</v>
       </c>
-      <c r="D98">
+      <c r="D98" s="6">
         <v>37653</v>
+      </c>
+      <c r="E98" s="66" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.35">
@@ -4447,54 +5045,63 @@
       <c r="C99" t="s">
         <v>4</v>
       </c>
-      <c r="D99">
+      <c r="D99" s="6">
         <v>37653</v>
       </c>
+      <c r="E99" s="66" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="60" t="s">
+      <c r="A100" t="s">
         <v>65</v>
       </c>
-      <c r="B100" s="60" t="s">
+      <c r="B100" t="s">
         <v>69</v>
       </c>
-      <c r="C100" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="D100" s="60">
+      <c r="C100" t="s">
+        <v>4</v>
+      </c>
+      <c r="D100" s="6">
         <v>37653</v>
       </c>
-      <c r="E100" s="56"/>
+      <c r="E100" s="66" t="s">
+        <v>465</v>
+      </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="56" t="s">
+      <c r="A101" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B101" s="56" t="s">
+      <c r="B101" s="46" t="s">
         <v>70</v>
       </c>
-      <c r="C101" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D101" s="56">
+      <c r="C101" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D101" s="70">
         <v>37653</v>
       </c>
-      <c r="E101" s="56"/>
+      <c r="E101" s="68" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A102" s="56" t="s">
+      <c r="A102" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B102" s="56" t="s">
+      <c r="B102" s="46" t="s">
         <v>71</v>
       </c>
-      <c r="C102" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D102" s="56">
+      <c r="C102" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D102" s="70">
         <v>37653</v>
       </c>
-      <c r="E102" s="56"/>
+      <c r="E102" s="68" t="s">
+        <v>467</v>
+      </c>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
@@ -4506,8 +5113,11 @@
       <c r="C103" t="s">
         <v>8</v>
       </c>
-      <c r="D103">
+      <c r="D103" s="6">
         <v>37653</v>
+      </c>
+      <c r="E103" s="66" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.35">
@@ -4520,8 +5130,11 @@
       <c r="C104" t="s">
         <v>8</v>
       </c>
-      <c r="D104">
+      <c r="D104" s="6">
         <v>37653</v>
+      </c>
+      <c r="E104" s="66" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.35">
@@ -4534,22 +5147,28 @@
       <c r="C105" t="s">
         <v>4</v>
       </c>
-      <c r="D105">
+      <c r="D105" s="6">
         <v>37653</v>
       </c>
+      <c r="E105" s="66" t="s">
+        <v>468</v>
+      </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="56" t="s">
+      <c r="A106" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B106" s="56" t="s">
+      <c r="B106" s="46" t="s">
         <v>73</v>
       </c>
-      <c r="C106" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D106" s="56">
+      <c r="C106" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D106" s="70">
         <v>37653</v>
+      </c>
+      <c r="E106" s="68" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.35">
@@ -4562,8 +5181,11 @@
       <c r="C107" t="s">
         <v>19</v>
       </c>
-      <c r="D107">
+      <c r="D107" s="6">
         <v>37653</v>
+      </c>
+      <c r="E107" s="66" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.35">
@@ -4576,64 +5198,79 @@
       <c r="C108" t="s">
         <v>8</v>
       </c>
-      <c r="D108">
+      <c r="D108" s="6">
         <v>37653</v>
       </c>
+      <c r="E108" s="66" t="s">
+        <v>470</v>
+      </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="56" t="s">
+      <c r="A109" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B109" s="56" t="s">
+      <c r="B109" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="C109" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D109" s="56">
+      <c r="C109" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D109" s="70">
         <v>37653</v>
       </c>
+      <c r="E109" s="68" t="s">
+        <v>472</v>
+      </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="56" t="s">
+      <c r="A110" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="B110" s="56" t="s">
+      <c r="B110" s="46" t="s">
         <v>76</v>
       </c>
-      <c r="C110" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D110" s="56">
+      <c r="C110" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D110" s="70">
         <v>37653</v>
       </c>
+      <c r="E110" s="68" t="s">
+        <v>473</v>
+      </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" t="s">
+      <c r="A111" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B111" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C111" t="s">
-        <v>8</v>
-      </c>
-      <c r="D111">
+      <c r="C111" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D111" s="71">
         <v>37653</v>
       </c>
+      <c r="E111" s="67" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" t="s">
+      <c r="A112" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B112" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C112" t="s">
-        <v>4</v>
-      </c>
-      <c r="D112">
+      <c r="C112" s="45" t="s">
+        <v>4</v>
+      </c>
+      <c r="D112" s="71">
         <v>37653</v>
+      </c>
+      <c r="E112" s="67" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.35">
@@ -4646,39 +5283,46 @@
       <c r="C113" t="s">
         <v>4</v>
       </c>
-      <c r="D113">
+      <c r="D113" s="6">
         <v>37653</v>
       </c>
+      <c r="E113" s="66" t="s">
+        <v>471</v>
+      </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="54" t="s">
+      <c r="A114" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B114" s="54" t="s">
+      <c r="B114" s="49" t="s">
         <v>12</v>
       </c>
-      <c r="C114" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D114" s="54">
+      <c r="C114" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D114" s="74">
         <v>41</v>
       </c>
-      <c r="E114" s="54"/>
+      <c r="E114" s="49" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="54" t="s">
+      <c r="A115" s="49" t="s">
         <v>77</v>
       </c>
-      <c r="B115" s="54" t="s">
+      <c r="B115" s="49" t="s">
         <v>78</v>
       </c>
-      <c r="C115" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D115" s="54">
+      <c r="C115" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D115" s="74">
         <v>41</v>
       </c>
-      <c r="E115" s="54"/>
+      <c r="E115" s="49" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
@@ -4690,8 +5334,11 @@
       <c r="C116" t="s">
         <v>4</v>
       </c>
-      <c r="D116">
+      <c r="D116" s="6">
         <v>53233</v>
+      </c>
+      <c r="E116" t="s">
+        <v>410</v>
       </c>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.35">
@@ -4704,8 +5351,11 @@
       <c r="C117" t="s">
         <v>4</v>
       </c>
-      <c r="D117">
+      <c r="D117" s="6">
         <v>53233</v>
+      </c>
+      <c r="E117" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.35">
@@ -4718,8 +5368,11 @@
       <c r="C118" t="s">
         <v>8</v>
       </c>
-      <c r="D118">
+      <c r="D118" s="6">
         <v>53233</v>
+      </c>
+      <c r="E118" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.35">
@@ -4732,8 +5385,11 @@
       <c r="C119" t="s">
         <v>8</v>
       </c>
-      <c r="D119">
+      <c r="D119" s="6">
         <v>53233</v>
+      </c>
+      <c r="E119" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.35">
@@ -4746,8 +5402,11 @@
       <c r="C120" t="s">
         <v>19</v>
       </c>
-      <c r="D120">
+      <c r="D120" s="6">
         <v>53233</v>
+      </c>
+      <c r="E120" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.35">
@@ -4760,8 +5419,11 @@
       <c r="C121" t="s">
         <v>8</v>
       </c>
-      <c r="D121">
+      <c r="D121" s="6">
         <v>53233</v>
+      </c>
+      <c r="E121" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.35">
@@ -4774,8 +5436,11 @@
       <c r="C122" t="s">
         <v>4</v>
       </c>
-      <c r="D122">
+      <c r="D122" s="6">
         <v>53233</v>
+      </c>
+      <c r="E122" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.35">
@@ -4788,159 +5453,180 @@
       <c r="C123" t="s">
         <v>4</v>
       </c>
-      <c r="D123">
+      <c r="D123" s="6">
         <v>53233</v>
       </c>
+      <c r="E123" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A124" s="54" t="s">
+      <c r="A124" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B124" s="54" t="s">
+      <c r="B124" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C124" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D124" s="54">
+      <c r="C124" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D124" s="69">
         <v>88</v>
       </c>
-      <c r="E124" s="54"/>
+      <c r="E124" s="44" t="s">
+        <v>410</v>
+      </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A125" s="54" t="s">
+      <c r="A125" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B125" s="54" t="s">
+      <c r="B125" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C125" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D125" s="54">
+      <c r="C125" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D125" s="69">
         <v>88</v>
       </c>
-      <c r="E125" s="54"/>
+      <c r="E125" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A126" s="54" t="s">
+      <c r="A126" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B126" s="54" t="s">
+      <c r="B126" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C126" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D126" s="54">
+      <c r="C126" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D126" s="69">
         <v>88</v>
       </c>
-      <c r="E126" s="54"/>
+      <c r="E126" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" s="54" t="s">
+      <c r="A127" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B127" s="54" t="s">
+      <c r="B127" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="C127" s="54" t="s">
+      <c r="C127" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="D127" s="54">
+      <c r="D127" s="69">
         <v>88</v>
       </c>
-      <c r="E127" s="54"/>
+      <c r="E127" s="44" t="s">
+        <v>411</v>
+      </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" s="54" t="s">
+      <c r="A128" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B128" s="54" t="s">
+      <c r="B128" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C128" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D128" s="54">
+      <c r="C128" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D128" s="69">
         <v>88</v>
       </c>
-      <c r="E128" s="54"/>
+      <c r="E128" s="44" t="s">
+        <v>413</v>
+      </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="54" t="s">
+      <c r="A129" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B129" s="54" t="s">
+      <c r="B129" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="C129" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D129" s="54">
+      <c r="C129" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D129" s="69">
         <v>88</v>
       </c>
-      <c r="E129" s="54"/>
+      <c r="E129" s="44" t="s">
+        <v>416</v>
+      </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="54" t="s">
+      <c r="A130" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B130" s="54" t="s">
+      <c r="B130" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="C130" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D130" s="54">
+      <c r="C130" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D130" s="69">
         <v>88</v>
       </c>
-      <c r="E130" s="54"/>
+      <c r="E130" s="44" t="s">
+        <v>455</v>
+      </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" s="54" t="s">
+      <c r="A131" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B131" s="54" t="s">
+      <c r="B131" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="C131" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D131" s="54">
+      <c r="C131" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D131" s="69">
         <v>88</v>
       </c>
-      <c r="E131" s="54"/>
+      <c r="E131" s="44" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A132" s="54" t="s">
+      <c r="A132" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B132" s="54" t="s">
+      <c r="B132" s="44" t="s">
         <v>81</v>
       </c>
-      <c r="C132" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D132" s="54">
+      <c r="C132" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D132" s="69">
         <v>88</v>
       </c>
-      <c r="E132" s="54"/>
+      <c r="E132" s="44"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A133" s="54" t="s">
+      <c r="A133" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="B133" s="54" t="s">
+      <c r="B133" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="C133" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D133" s="54">
+      <c r="C133" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D133" s="69">
         <v>88</v>
       </c>
-      <c r="E133" s="54"/>
+      <c r="E133" s="44" t="s">
+        <v>475</v>
+      </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
@@ -4952,8 +5638,11 @@
       <c r="C134" t="s">
         <v>4</v>
       </c>
-      <c r="D134">
+      <c r="D134" s="6">
         <v>41</v>
+      </c>
+      <c r="E134" s="64" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.35">
@@ -4966,143 +5655,165 @@
       <c r="C135" t="s">
         <v>8</v>
       </c>
-      <c r="D135">
+      <c r="D135" s="6">
         <v>41</v>
       </c>
+      <c r="E135" s="64" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A136" t="s">
+      <c r="A136" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="B136" t="s">
+      <c r="B136" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="C136" t="s">
-        <v>8</v>
-      </c>
-      <c r="D136">
+      <c r="C136" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="D136" s="71">
         <v>41</v>
       </c>
+      <c r="E136" s="45" t="s">
+        <v>476</v>
+      </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A137" s="54" t="s">
+      <c r="A137" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B137" s="54" t="s">
+      <c r="B137" s="49" t="s">
         <v>85</v>
       </c>
-      <c r="C137" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D137" s="54">
+      <c r="C137" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D137" s="74">
         <v>138</v>
       </c>
-      <c r="E137" s="54"/>
+      <c r="E137" s="49" t="s">
+        <v>477</v>
+      </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A138" s="54" t="s">
+      <c r="A138" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B138" s="54" t="s">
+      <c r="B138" s="49" t="s">
         <v>86</v>
       </c>
-      <c r="C138" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D138" s="54">
+      <c r="C138" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D138" s="74">
         <v>138</v>
       </c>
-      <c r="E138" s="54"/>
+      <c r="E138" s="49" t="s">
+        <v>478</v>
+      </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A139" s="54" t="s">
+      <c r="A139" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B139" s="54" t="s">
+      <c r="B139" s="49" t="s">
         <v>87</v>
       </c>
-      <c r="C139" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D139" s="54">
+      <c r="C139" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D139" s="74">
         <v>138</v>
       </c>
-      <c r="E139" s="54"/>
+      <c r="E139" s="49" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A140" s="54" t="s">
+      <c r="A140" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B140" s="54" t="s">
+      <c r="B140" s="49" t="s">
         <v>88</v>
       </c>
-      <c r="C140" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D140" s="54">
+      <c r="C140" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D140" s="74">
         <v>138</v>
       </c>
-      <c r="E140" s="54"/>
+      <c r="E140" s="49" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A141" s="54" t="s">
+      <c r="A141" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B141" s="54" t="s">
+      <c r="B141" s="49" t="s">
         <v>89</v>
       </c>
-      <c r="C141" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D141" s="54">
+      <c r="C141" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D141" s="74">
         <v>138</v>
       </c>
-      <c r="E141" s="54"/>
+      <c r="E141" s="49" t="s">
+        <v>480</v>
+      </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A142" s="54" t="s">
+      <c r="A142" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B142" s="54" t="s">
+      <c r="B142" s="49" t="s">
         <v>90</v>
       </c>
-      <c r="C142" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D142" s="54">
+      <c r="C142" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D142" s="74">
         <v>138</v>
       </c>
-      <c r="E142" s="54"/>
+      <c r="E142" s="49" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A143" s="54" t="s">
+      <c r="A143" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B143" s="54" t="s">
+      <c r="B143" s="49" t="s">
         <v>91</v>
       </c>
-      <c r="C143" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D143" s="54">
+      <c r="C143" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D143" s="74">
         <v>138</v>
       </c>
-      <c r="E143" s="54"/>
+      <c r="E143" s="49" t="s">
+        <v>481</v>
+      </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A144" s="54" t="s">
+      <c r="A144" s="49" t="s">
         <v>84</v>
       </c>
-      <c r="B144" s="54" t="s">
+      <c r="B144" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C144" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D144" s="54">
+      <c r="C144" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D144" s="74">
         <v>138</v>
       </c>
-      <c r="E144" s="54"/>
+      <c r="E144" s="49" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
@@ -5114,8 +5825,11 @@
       <c r="C145" t="s">
         <v>4</v>
       </c>
-      <c r="D145">
+      <c r="D145" s="6">
         <v>670</v>
+      </c>
+      <c r="E145" s="64" t="s">
+        <v>477</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.35">
@@ -5128,8 +5842,11 @@
       <c r="C146" t="s">
         <v>4</v>
       </c>
-      <c r="D146">
+      <c r="D146" s="6">
         <v>670</v>
+      </c>
+      <c r="E146" s="64" t="s">
+        <v>478</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.35">
@@ -5142,8 +5859,11 @@
       <c r="C147" t="s">
         <v>8</v>
       </c>
-      <c r="D147">
+      <c r="D147" s="6">
         <v>670</v>
+      </c>
+      <c r="E147" s="64" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.35">
@@ -5156,8 +5876,11 @@
       <c r="C148" t="s">
         <v>8</v>
       </c>
-      <c r="D148">
+      <c r="D148" s="6">
         <v>670</v>
+      </c>
+      <c r="E148" s="64" t="s">
+        <v>479</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.35">
@@ -5170,8 +5893,11 @@
       <c r="C149" t="s">
         <v>4</v>
       </c>
-      <c r="D149">
+      <c r="D149" s="6">
         <v>670</v>
+      </c>
+      <c r="E149" s="64" t="s">
+        <v>480</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.35">
@@ -5184,8 +5910,11 @@
       <c r="C150" t="s">
         <v>8</v>
       </c>
-      <c r="D150">
+      <c r="D150" s="6">
         <v>670</v>
+      </c>
+      <c r="E150" s="64" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.35">
@@ -5198,8 +5927,11 @@
       <c r="C151" t="s">
         <v>8</v>
       </c>
-      <c r="D151">
+      <c r="D151" s="6">
         <v>670</v>
+      </c>
+      <c r="E151" s="64" t="s">
+        <v>481</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.35">
@@ -5212,1759 +5944,1774 @@
       <c r="C152" t="s">
         <v>8</v>
       </c>
-      <c r="D152">
+      <c r="D152" s="6">
         <v>670</v>
       </c>
+      <c r="E152" s="64" t="s">
+        <v>482</v>
+      </c>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A153" s="55" t="s">
+      <c r="A153" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="B153" s="55" t="s">
+      <c r="B153" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="C153" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D153" s="55">
+      <c r="C153" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D153" s="72">
         <v>670</v>
       </c>
-      <c r="E153" s="55" t="s">
-        <v>395</v>
+      <c r="E153" s="47" t="s">
+        <v>387</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A154" s="55" t="s">
+      <c r="A154" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="B154" s="55" t="s">
+      <c r="B154" s="47" t="s">
         <v>94</v>
       </c>
-      <c r="C154" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D154" s="55">
+      <c r="C154" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D154" s="72">
         <v>670</v>
       </c>
-      <c r="E154" s="55" t="s">
-        <v>399</v>
+      <c r="E154" s="47" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A155" s="56" t="s">
+      <c r="A155" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="B155" s="56" t="s">
+      <c r="B155" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="C155" s="56" t="s">
-        <v>4</v>
-      </c>
-      <c r="D155" s="56">
+      <c r="C155" s="46" t="s">
+        <v>4</v>
+      </c>
+      <c r="D155" s="70">
         <v>670</v>
       </c>
-      <c r="E155" s="56" t="s">
-        <v>398</v>
+      <c r="E155" s="46" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A156" s="55" t="s">
+      <c r="A156" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="B156" s="55" t="s">
+      <c r="B156" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="C156" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D156" s="55">
+      <c r="C156" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D156" s="72">
         <v>670</v>
       </c>
-      <c r="E156" s="55" t="s">
-        <v>397</v>
+      <c r="E156" s="47" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A157" s="55" t="s">
+      <c r="A157" s="47" t="s">
         <v>93</v>
       </c>
-      <c r="B157" s="55" t="s">
+      <c r="B157" s="47" t="s">
         <v>63</v>
       </c>
-      <c r="C157" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D157" s="55">
+      <c r="C157" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D157" s="72">
         <v>670</v>
       </c>
-      <c r="E157" s="55" t="s">
-        <v>393</v>
+      <c r="E157" s="47" t="s">
+        <v>385</v>
       </c>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A158" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="B158" s="59" t="s">
+      <c r="A158" s="76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B158" s="76" t="s">
         <v>98</v>
       </c>
-      <c r="C158" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D158" s="59">
-        <v>3819</v>
-      </c>
-      <c r="E158" s="59"/>
+      <c r="C158" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D158" s="77">
+        <v>3819</v>
+      </c>
+      <c r="E158" s="76" t="s">
+        <v>484</v>
+      </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A159" s="59" t="s">
-        <v>97</v>
-      </c>
-      <c r="B159" s="59" t="s">
+      <c r="A159" s="76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B159" s="76" t="s">
         <v>99</v>
       </c>
-      <c r="C159" s="59" t="s">
-        <v>4</v>
-      </c>
-      <c r="D159" s="59">
-        <v>3819</v>
-      </c>
-      <c r="E159" s="59"/>
+      <c r="C159" s="76" t="s">
+        <v>4</v>
+      </c>
+      <c r="D159" s="77">
+        <v>3819</v>
+      </c>
+      <c r="E159" s="76" t="s">
+        <v>485</v>
+      </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A160" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B160" s="61" t="s">
+      <c r="A160" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B160" s="50" t="s">
         <v>100</v>
       </c>
-      <c r="C160" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D160" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E160" s="61"/>
+      <c r="C160" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D160" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E160" s="50"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A161" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B161" s="61" t="s">
+      <c r="A161" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B161" s="50" t="s">
         <v>101</v>
       </c>
-      <c r="C161" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E161" s="61"/>
+      <c r="C161" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D161" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E161" s="50"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A162" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B162" s="61" t="s">
+      <c r="A162" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B162" s="50" t="s">
         <v>102</v>
       </c>
-      <c r="C162" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D162" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E162" s="61"/>
+      <c r="C162" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D162" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E162" s="50"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A163" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B163" s="54" t="s">
+      <c r="A163" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B163" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C163" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D163" s="54">
-        <v>3819</v>
-      </c>
-      <c r="E163" s="54"/>
+      <c r="C163" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D163" s="69">
+        <v>3819</v>
+      </c>
+      <c r="E163" s="44" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A164" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B164" s="61" t="s">
+      <c r="A164" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B164" s="50" t="s">
         <v>103</v>
       </c>
-      <c r="C164" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D164" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E164" s="61"/>
+      <c r="C164" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D164" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E164" s="50"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A165" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B165" s="61" t="s">
+      <c r="A165" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B165" s="50" t="s">
         <v>104</v>
       </c>
-      <c r="C165" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D165" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E165" s="61"/>
+      <c r="C165" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D165" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E165" s="50"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A166" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B166" s="54" t="s">
+      <c r="A166" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B166" s="44" t="s">
         <v>105</v>
       </c>
-      <c r="C166" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D166" s="54">
-        <v>3819</v>
-      </c>
-      <c r="E166" s="54"/>
+      <c r="C166" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D166" s="69">
+        <v>3819</v>
+      </c>
+      <c r="E166" s="44" t="s">
+        <v>415</v>
+      </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A167" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B167" s="61" t="s">
+      <c r="A167" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B167" s="50" t="s">
         <v>106</v>
       </c>
-      <c r="C167" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D167" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E167" s="61"/>
+      <c r="C167" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D167" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E167" s="50"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A168" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B168" s="61" t="s">
+      <c r="A168" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B168" s="50" t="s">
         <v>107</v>
       </c>
-      <c r="C168" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D168" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E168" s="61"/>
+      <c r="C168" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D168" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E168" s="50"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A169" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B169" s="61" t="s">
+      <c r="A169" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B169" s="50" t="s">
         <v>108</v>
       </c>
-      <c r="C169" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D169" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E169" s="61"/>
+      <c r="C169" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D169" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E169" s="50"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A170" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B170" s="61" t="s">
+      <c r="A170" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B170" s="50" t="s">
         <v>109</v>
       </c>
-      <c r="C170" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D170" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E170" s="61"/>
+      <c r="C170" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D170" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E170" s="50"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A171" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B171" s="61" t="s">
+      <c r="A171" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B171" s="50" t="s">
         <v>110</v>
       </c>
-      <c r="C171" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D171" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E171" s="61"/>
+      <c r="C171" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D171" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E171" s="50"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A172" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B172" s="61" t="s">
+      <c r="A172" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B172" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="C172" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D172" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E172" s="61"/>
+      <c r="C172" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D172" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E172" s="50"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A173" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B173" s="61" t="s">
+      <c r="A173" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B173" s="50" t="s">
         <v>112</v>
       </c>
-      <c r="C173" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D173" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E173" s="61"/>
+      <c r="C173" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D173" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E173" s="50"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A174" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B174" s="61" t="s">
+      <c r="A174" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B174" s="50" t="s">
         <v>113</v>
       </c>
-      <c r="C174" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D174" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E174" s="61"/>
+      <c r="C174" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D174" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E174" s="50"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A175" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B175" s="61" t="s">
+      <c r="A175" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B175" s="50" t="s">
         <v>114</v>
       </c>
-      <c r="C175" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D175" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E175" s="61"/>
+      <c r="C175" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D175" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E175" s="50"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A176" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B176" s="61" t="s">
+      <c r="A176" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B176" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="C176" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D176" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E176" s="61"/>
+      <c r="C176" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D176" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E176" s="50"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A177" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B177" s="61" t="s">
+      <c r="A177" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B177" s="50" t="s">
         <v>116</v>
       </c>
-      <c r="C177" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D177" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E177" s="61"/>
+      <c r="C177" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D177" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E177" s="50"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A178" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B178" s="61" t="s">
+      <c r="A178" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B178" s="50" t="s">
         <v>117</v>
       </c>
-      <c r="C178" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D178" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E178" s="61"/>
+      <c r="C178" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D178" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E178" s="50"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A179" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B179" s="61" t="s">
+      <c r="A179" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B179" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="C179" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D179" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E179" s="61"/>
+      <c r="C179" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D179" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E179" s="50"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A180" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B180" s="61" t="s">
+      <c r="A180" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B180" s="50" t="s">
         <v>119</v>
       </c>
-      <c r="C180" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D180" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E180" s="61"/>
+      <c r="C180" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D180" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E180" s="50"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A181" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B181" s="61" t="s">
+      <c r="A181" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B181" s="50" t="s">
         <v>120</v>
       </c>
-      <c r="C181" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D181" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E181" s="61"/>
+      <c r="C181" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D181" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E181" s="50"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A182" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B182" s="61" t="s">
+      <c r="A182" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B182" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="C182" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D182" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E182" s="61"/>
+      <c r="C182" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D182" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E182" s="50"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A183" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B183" s="61" t="s">
+      <c r="A183" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B183" s="50" t="s">
         <v>122</v>
       </c>
-      <c r="C183" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D183" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E183" s="61"/>
+      <c r="C183" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D183" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E183" s="50"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A184" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B184" s="61" t="s">
+      <c r="A184" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B184" s="50" t="s">
         <v>123</v>
       </c>
-      <c r="C184" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D184" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E184" s="61"/>
+      <c r="C184" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D184" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E184" s="50"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A185" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B185" s="61" t="s">
+      <c r="A185" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B185" s="50" t="s">
         <v>124</v>
       </c>
-      <c r="C185" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D185" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E185" s="61"/>
+      <c r="C185" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D185" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E185" s="50"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A186" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B186" s="61" t="s">
+      <c r="A186" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B186" s="50" t="s">
         <v>125</v>
       </c>
-      <c r="C186" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D186" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E186" s="61"/>
+      <c r="C186" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D186" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E186" s="50"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A187" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B187" s="61" t="s">
+      <c r="A187" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B187" s="50" t="s">
         <v>126</v>
       </c>
-      <c r="C187" s="61" t="s">
-        <v>8</v>
-      </c>
-      <c r="D187" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E187" s="61"/>
+      <c r="C187" s="50" t="s">
+        <v>8</v>
+      </c>
+      <c r="D187" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E187" s="50"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A188" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B188" s="61" t="s">
+      <c r="A188" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B188" s="50" t="s">
         <v>127</v>
       </c>
-      <c r="C188" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D188" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E188" s="61"/>
+      <c r="C188" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D188" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E188" s="50"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A189" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B189" s="61" t="s">
+      <c r="A189" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B189" s="50" t="s">
         <v>128</v>
       </c>
-      <c r="C189" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D189" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E189" s="61"/>
+      <c r="C189" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D189" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E189" s="50"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A190" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B190" s="61" t="s">
+      <c r="A190" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B190" s="50" t="s">
         <v>129</v>
       </c>
-      <c r="C190" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D190" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E190" s="61"/>
+      <c r="C190" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D190" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E190" s="50"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A191" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B191" s="61" t="s">
+      <c r="A191" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B191" s="50" t="s">
         <v>130</v>
       </c>
-      <c r="C191" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D191" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E191" s="61"/>
+      <c r="C191" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D191" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E191" s="50"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A192" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B192" s="61" t="s">
+      <c r="A192" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B192" s="50" t="s">
         <v>131</v>
       </c>
-      <c r="C192" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D192" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E192" s="61"/>
+      <c r="C192" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D192" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E192" s="50"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A193" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B193" s="61" t="s">
+      <c r="A193" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B193" s="50" t="s">
         <v>132</v>
       </c>
-      <c r="C193" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D193" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E193" s="61"/>
+      <c r="C193" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D193" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E193" s="50"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A194" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B194" s="61" t="s">
+      <c r="A194" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B194" s="50" t="s">
         <v>133</v>
       </c>
-      <c r="C194" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D194" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E194" s="61"/>
+      <c r="C194" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D194" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E194" s="50"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A195" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B195" s="61" t="s">
+      <c r="A195" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B195" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="C195" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D195" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E195" s="61"/>
+      <c r="C195" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D195" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E195" s="50"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A196" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B196" s="61" t="s">
+      <c r="A196" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B196" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="C196" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D196" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E196" s="61"/>
+      <c r="C196" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D196" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E196" s="50"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A197" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B197" s="61" t="s">
+      <c r="A197" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B197" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="C197" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D197" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E197" s="61"/>
+      <c r="C197" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D197" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E197" s="50"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A198" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B198" s="61" t="s">
+      <c r="A198" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B198" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="C198" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D198" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E198" s="61"/>
+      <c r="C198" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D198" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E198" s="50"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A199" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B199" s="61" t="s">
+      <c r="A199" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B199" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="C199" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D199" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E199" s="61"/>
+      <c r="C199" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D199" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E199" s="50"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A200" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B200" s="61" t="s">
+      <c r="A200" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B200" s="50" t="s">
         <v>139</v>
       </c>
-      <c r="C200" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D200" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E200" s="61"/>
+      <c r="C200" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D200" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E200" s="50"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A201" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B201" s="61" t="s">
+      <c r="A201" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B201" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="C201" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D201" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E201" s="61"/>
+      <c r="C201" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D201" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E201" s="50"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A202" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B202" s="61" t="s">
+      <c r="A202" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B202" s="50" t="s">
         <v>141</v>
       </c>
-      <c r="C202" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D202" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E202" s="61"/>
+      <c r="C202" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D202" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E202" s="50"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A203" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B203" s="61" t="s">
+      <c r="A203" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B203" s="50" t="s">
         <v>142</v>
       </c>
-      <c r="C203" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D203" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E203" s="61"/>
+      <c r="C203" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D203" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E203" s="50"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A204" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B204" s="61" t="s">
+      <c r="A204" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B204" s="50" t="s">
         <v>143</v>
       </c>
-      <c r="C204" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D204" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E204" s="61"/>
+      <c r="C204" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D204" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E204" s="50"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A205" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B205" s="61" t="s">
+      <c r="A205" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B205" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C205" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D205" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E205" s="61"/>
+      <c r="C205" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D205" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E205" s="50"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A206" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B206" s="61" t="s">
+      <c r="A206" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B206" s="50" t="s">
         <v>145</v>
       </c>
-      <c r="C206" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D206" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E206" s="61"/>
+      <c r="C206" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D206" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E206" s="50"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A207" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B207" s="61" t="s">
+      <c r="A207" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B207" s="50" t="s">
         <v>146</v>
       </c>
-      <c r="C207" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D207" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E207" s="61"/>
+      <c r="C207" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D207" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E207" s="50"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A208" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B208" s="61" t="s">
+      <c r="A208" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B208" s="50" t="s">
         <v>147</v>
       </c>
-      <c r="C208" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D208" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E208" s="61"/>
+      <c r="C208" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D208" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E208" s="50"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A209" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B209" s="61" t="s">
+      <c r="A209" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B209" s="50" t="s">
         <v>148</v>
       </c>
-      <c r="C209" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D209" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E209" s="61"/>
+      <c r="C209" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D209" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E209" s="50"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A210" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B210" s="61" t="s">
+      <c r="A210" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B210" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="C210" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D210" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E210" s="61"/>
+      <c r="C210" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D210" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E210" s="50"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A211" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B211" s="61" t="s">
+      <c r="A211" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B211" s="50" t="s">
         <v>150</v>
       </c>
-      <c r="C211" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D211" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E211" s="61"/>
+      <c r="C211" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D211" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E211" s="50"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A212" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B212" s="61" t="s">
+      <c r="A212" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B212" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="C212" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D212" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E212" s="61"/>
+      <c r="C212" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D212" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E212" s="50"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A213" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B213" s="61" t="s">
+      <c r="A213" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B213" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="C213" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D213" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E213" s="61"/>
+      <c r="C213" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D213" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E213" s="50"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A214" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B214" s="61" t="s">
+      <c r="A214" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B214" s="50" t="s">
         <v>153</v>
       </c>
-      <c r="C214" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D214" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E214" s="61"/>
+      <c r="C214" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D214" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E214" s="50"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A215" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B215" s="61" t="s">
+      <c r="A215" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B215" s="50" t="s">
         <v>154</v>
       </c>
-      <c r="C215" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D215" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E215" s="61"/>
+      <c r="C215" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D215" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E215" s="50"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A216" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B216" s="61" t="s">
+      <c r="A216" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B216" s="50" t="s">
         <v>155</v>
       </c>
-      <c r="C216" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D216" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E216" s="61"/>
+      <c r="C216" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D216" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E216" s="50"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A217" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B217" s="61" t="s">
+      <c r="A217" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B217" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C217" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D217" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E217" s="61"/>
+      <c r="C217" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D217" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E217" s="50"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A218" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B218" s="61" t="s">
+      <c r="A218" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B218" s="50" t="s">
         <v>157</v>
       </c>
-      <c r="C218" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D218" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E218" s="61"/>
+      <c r="C218" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D218" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E218" s="50"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A219" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B219" s="61" t="s">
+      <c r="A219" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B219" s="50" t="s">
         <v>158</v>
       </c>
-      <c r="C219" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D219" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E219" s="61"/>
+      <c r="C219" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D219" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E219" s="50"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A220" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B220" s="61" t="s">
+      <c r="A220" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B220" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="C220" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D220" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E220" s="61"/>
+      <c r="C220" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D220" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E220" s="50"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A221" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B221" s="61" t="s">
+      <c r="A221" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B221" s="50" t="s">
         <v>160</v>
       </c>
-      <c r="C221" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D221" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E221" s="61"/>
+      <c r="C221" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D221" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E221" s="50"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A222" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B222" s="61" t="s">
+      <c r="A222" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B222" s="50" t="s">
         <v>161</v>
       </c>
-      <c r="C222" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D222" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E222" s="61"/>
+      <c r="C222" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D222" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E222" s="50"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A223" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B223" s="61" t="s">
+      <c r="A223" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B223" s="50" t="s">
         <v>162</v>
       </c>
-      <c r="C223" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D223" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E223" s="61"/>
+      <c r="C223" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D223" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E223" s="50"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A224" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B224" s="61" t="s">
+      <c r="A224" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B224" s="50" t="s">
         <v>163</v>
       </c>
-      <c r="C224" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D224" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E224" s="61"/>
+      <c r="C224" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D224" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E224" s="50"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A225" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B225" s="61" t="s">
+      <c r="A225" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B225" s="50" t="s">
         <v>164</v>
       </c>
-      <c r="C225" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D225" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E225" s="61"/>
+      <c r="C225" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D225" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E225" s="50"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A226" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B226" s="61" t="s">
+      <c r="A226" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B226" s="50" t="s">
         <v>165</v>
       </c>
-      <c r="C226" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D226" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E226" s="61"/>
+      <c r="C226" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D226" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E226" s="50"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A227" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B227" s="61" t="s">
+      <c r="A227" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B227" s="50" t="s">
         <v>166</v>
       </c>
-      <c r="C227" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D227" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E227" s="61"/>
+      <c r="C227" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D227" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E227" s="50"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A228" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B228" s="61" t="s">
+      <c r="A228" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B228" s="50" t="s">
         <v>167</v>
       </c>
-      <c r="C228" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D228" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E228" s="61"/>
+      <c r="C228" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D228" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E228" s="50"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A229" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B229" s="61" t="s">
+      <c r="A229" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B229" s="50" t="s">
         <v>168</v>
       </c>
-      <c r="C229" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D229" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E229" s="61"/>
+      <c r="C229" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D229" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E229" s="50"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A230" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B230" s="61" t="s">
+      <c r="A230" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B230" s="50" t="s">
         <v>169</v>
       </c>
-      <c r="C230" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D230" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E230" s="61"/>
+      <c r="C230" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D230" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E230" s="50"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A231" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B231" s="61" t="s">
+      <c r="A231" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B231" s="50" t="s">
         <v>170</v>
       </c>
-      <c r="C231" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D231" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E231" s="61"/>
+      <c r="C231" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D231" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E231" s="50"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A232" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B232" s="61" t="s">
+      <c r="A232" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B232" s="50" t="s">
         <v>171</v>
       </c>
-      <c r="C232" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D232" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E232" s="61"/>
+      <c r="C232" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D232" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E232" s="50"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A233" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B233" s="61" t="s">
+      <c r="A233" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B233" s="50" t="s">
         <v>172</v>
       </c>
-      <c r="C233" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D233" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E233" s="61"/>
+      <c r="C233" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D233" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E233" s="50"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A234" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B234" s="61" t="s">
+      <c r="A234" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B234" s="50" t="s">
         <v>173</v>
       </c>
-      <c r="C234" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D234" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E234" s="61"/>
+      <c r="C234" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D234" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E234" s="50"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A235" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B235" s="61" t="s">
+      <c r="A235" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B235" s="50" t="s">
         <v>174</v>
       </c>
-      <c r="C235" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D235" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E235" s="61"/>
+      <c r="C235" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D235" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E235" s="50"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A236" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B236" s="61" t="s">
+      <c r="A236" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B236" s="50" t="s">
         <v>175</v>
       </c>
-      <c r="C236" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D236" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E236" s="61"/>
+      <c r="C236" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D236" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E236" s="50"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A237" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B237" s="61" t="s">
+      <c r="A237" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B237" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="C237" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D237" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E237" s="61"/>
+      <c r="C237" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D237" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E237" s="50"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A238" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B238" s="61" t="s">
+      <c r="A238" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B238" s="50" t="s">
         <v>177</v>
       </c>
-      <c r="C238" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D238" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E238" s="61"/>
+      <c r="C238" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D238" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E238" s="50"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A239" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B239" s="61" t="s">
+      <c r="A239" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B239" s="50" t="s">
         <v>178</v>
       </c>
-      <c r="C239" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D239" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E239" s="61"/>
+      <c r="C239" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D239" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E239" s="50"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A240" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B240" s="61" t="s">
+      <c r="A240" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B240" s="50" t="s">
         <v>179</v>
       </c>
-      <c r="C240" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D240" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E240" s="61"/>
+      <c r="C240" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D240" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E240" s="50"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A241" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B241" s="61" t="s">
+      <c r="A241" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B241" s="50" t="s">
         <v>180</v>
       </c>
-      <c r="C241" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D241" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E241" s="61"/>
+      <c r="C241" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D241" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E241" s="50"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A242" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B242" s="61" t="s">
+      <c r="A242" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B242" s="50" t="s">
         <v>181</v>
       </c>
-      <c r="C242" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D242" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E242" s="61"/>
+      <c r="C242" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D242" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E242" s="50"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A243" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B243" s="61" t="s">
+      <c r="A243" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B243" s="50" t="s">
         <v>182</v>
       </c>
-      <c r="C243" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D243" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E243" s="61"/>
+      <c r="C243" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D243" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E243" s="50"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A244" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B244" s="61" t="s">
+      <c r="A244" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B244" s="50" t="s">
         <v>183</v>
       </c>
-      <c r="C244" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D244" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E244" s="61"/>
+      <c r="C244" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D244" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E244" s="50"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A245" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B245" s="61" t="s">
+      <c r="A245" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B245" s="50" t="s">
         <v>184</v>
       </c>
-      <c r="C245" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D245" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E245" s="61"/>
+      <c r="C245" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D245" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E245" s="50"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A246" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B246" s="61" t="s">
+      <c r="A246" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B246" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="C246" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D246" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E246" s="61"/>
+      <c r="C246" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D246" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E246" s="50"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A247" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B247" s="61" t="s">
+      <c r="A247" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B247" s="50" t="s">
         <v>186</v>
       </c>
-      <c r="C247" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D247" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E247" s="61"/>
+      <c r="C247" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D247" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E247" s="50"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A248" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B248" s="61" t="s">
+      <c r="A248" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B248" s="50" t="s">
         <v>187</v>
       </c>
-      <c r="C248" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D248" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E248" s="61"/>
+      <c r="C248" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D248" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E248" s="50"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A249" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B249" s="61" t="s">
+      <c r="A249" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B249" s="50" t="s">
         <v>188</v>
       </c>
-      <c r="C249" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D249" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E249" s="61"/>
+      <c r="C249" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D249" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E249" s="50"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A250" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B250" s="61" t="s">
+      <c r="A250" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B250" s="50" t="s">
         <v>189</v>
       </c>
-      <c r="C250" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D250" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E250" s="61"/>
+      <c r="C250" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D250" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E250" s="50"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A251" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B251" s="61" t="s">
+      <c r="A251" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B251" s="50" t="s">
         <v>190</v>
       </c>
-      <c r="C251" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D251" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E251" s="61"/>
+      <c r="C251" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D251" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E251" s="50"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A252" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B252" s="61" t="s">
+      <c r="A252" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B252" s="50" t="s">
         <v>191</v>
       </c>
-      <c r="C252" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D252" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E252" s="61"/>
+      <c r="C252" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D252" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E252" s="50"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A253" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B253" s="61" t="s">
+      <c r="A253" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B253" s="50" t="s">
         <v>192</v>
       </c>
-      <c r="C253" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D253" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E253" s="61"/>
+      <c r="C253" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D253" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E253" s="50"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A254" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B254" s="61" t="s">
+      <c r="A254" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B254" s="50" t="s">
         <v>193</v>
       </c>
-      <c r="C254" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D254" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E254" s="61"/>
+      <c r="C254" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D254" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E254" s="50"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A255" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B255" s="61" t="s">
+      <c r="A255" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B255" s="50" t="s">
         <v>194</v>
       </c>
-      <c r="C255" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D255" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E255" s="61"/>
+      <c r="C255" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D255" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E255" s="50"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A256" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B256" s="61" t="s">
+      <c r="A256" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B256" s="50" t="s">
         <v>195</v>
       </c>
-      <c r="C256" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D256" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E256" s="61"/>
+      <c r="C256" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D256" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E256" s="50"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A257" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B257" s="61" t="s">
+      <c r="A257" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B257" s="50" t="s">
         <v>196</v>
       </c>
-      <c r="C257" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D257" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E257" s="61"/>
+      <c r="C257" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D257" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E257" s="50"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A258" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B258" s="61" t="s">
+      <c r="A258" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B258" s="50" t="s">
         <v>197</v>
       </c>
-      <c r="C258" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D258" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E258" s="61"/>
+      <c r="C258" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D258" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E258" s="50"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A259" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B259" s="61" t="s">
+      <c r="A259" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B259" s="50" t="s">
         <v>198</v>
       </c>
-      <c r="C259" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D259" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E259" s="61"/>
+      <c r="C259" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D259" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E259" s="50"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A260" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B260" s="61" t="s">
+      <c r="A260" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B260" s="50" t="s">
         <v>199</v>
       </c>
-      <c r="C260" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D260" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E260" s="61"/>
+      <c r="C260" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D260" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E260" s="50"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A261" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B261" s="61" t="s">
+      <c r="A261" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B261" s="50" t="s">
         <v>200</v>
       </c>
-      <c r="C261" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D261" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E261" s="61"/>
+      <c r="C261" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D261" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E261" s="50"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A262" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B262" s="61" t="s">
+      <c r="A262" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B262" s="50" t="s">
         <v>201</v>
       </c>
-      <c r="C262" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D262" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E262" s="61"/>
+      <c r="C262" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D262" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E262" s="50"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A263" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B263" s="61" t="s">
+      <c r="A263" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B263" s="50" t="s">
         <v>202</v>
       </c>
-      <c r="C263" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D263" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E263" s="61"/>
+      <c r="C263" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D263" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E263" s="50"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A264" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B264" s="61" t="s">
+      <c r="A264" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B264" s="50" t="s">
         <v>203</v>
       </c>
-      <c r="C264" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D264" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E264" s="61"/>
+      <c r="C264" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D264" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E264" s="50"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A265" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B265" s="61" t="s">
+      <c r="A265" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B265" s="50" t="s">
         <v>204</v>
       </c>
-      <c r="C265" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D265" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E265" s="61"/>
+      <c r="C265" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D265" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E265" s="50"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A266" s="61" t="s">
-        <v>97</v>
-      </c>
-      <c r="B266" s="61" t="s">
+      <c r="A266" s="50" t="s">
+        <v>97</v>
+      </c>
+      <c r="B266" s="50" t="s">
         <v>205</v>
       </c>
-      <c r="C266" s="61" t="s">
-        <v>4</v>
-      </c>
-      <c r="D266" s="61">
-        <v>3819</v>
-      </c>
-      <c r="E266" s="61"/>
+      <c r="C266" s="50" t="s">
+        <v>4</v>
+      </c>
+      <c r="D266" s="73">
+        <v>3819</v>
+      </c>
+      <c r="E266" s="50"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A267" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B267" s="54" t="s">
+      <c r="A267" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B267" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="C267" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D267" s="54">
-        <v>3819</v>
-      </c>
-      <c r="E267" s="54"/>
+      <c r="C267" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D267" s="69">
+        <v>3819</v>
+      </c>
+      <c r="E267" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A268" s="54" t="s">
-        <v>97</v>
-      </c>
-      <c r="B268" s="54" t="s">
+      <c r="A268" s="44" t="s">
+        <v>97</v>
+      </c>
+      <c r="B268" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="C268" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D268" s="54">
-        <v>3819</v>
-      </c>
-      <c r="E268" s="54"/>
+      <c r="C268" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D268" s="69">
+        <v>3819</v>
+      </c>
+      <c r="E268" s="44" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A269" t="s">
@@ -6976,8 +7723,11 @@
       <c r="C269" t="s">
         <v>4</v>
       </c>
-      <c r="D269">
+      <c r="D269" s="6">
         <v>49</v>
+      </c>
+      <c r="E269" t="s">
+        <v>487</v>
       </c>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.35">
@@ -6990,8 +7740,11 @@
       <c r="C270" t="s">
         <v>4</v>
       </c>
-      <c r="D270">
+      <c r="D270" s="6">
         <v>49</v>
+      </c>
+      <c r="E270" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.35">
@@ -7004,8 +7757,11 @@
       <c r="C271" t="s">
         <v>4</v>
       </c>
-      <c r="D271">
+      <c r="D271" s="6">
         <v>49</v>
+      </c>
+      <c r="E271" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.35">
@@ -7018,8 +7774,11 @@
       <c r="C272" t="s">
         <v>8</v>
       </c>
-      <c r="D272">
+      <c r="D272" s="6">
         <v>49</v>
+      </c>
+      <c r="E272" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.35">
@@ -7032,8 +7791,11 @@
       <c r="C273" t="s">
         <v>8</v>
       </c>
-      <c r="D273">
+      <c r="D273" s="6">
         <v>49</v>
+      </c>
+      <c r="E273" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.35">
@@ -7046,115 +7808,130 @@
       <c r="C274" t="s">
         <v>4</v>
       </c>
-      <c r="D274">
+      <c r="D274" s="6">
         <v>49</v>
       </c>
+      <c r="E274" t="s">
+        <v>489</v>
+      </c>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A275" s="54" t="s">
+      <c r="A275" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B275" s="54" t="s">
+      <c r="B275" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C275" s="54" t="s">
+      <c r="C275" s="49" t="s">
         <v>19</v>
       </c>
-      <c r="D275" s="54">
+      <c r="D275" s="74">
         <v>336</v>
       </c>
-      <c r="E275" s="54"/>
+      <c r="E275" s="49" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A276" s="54" t="s">
+      <c r="A276" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B276" s="54" t="s">
+      <c r="B276" s="49" t="s">
         <v>209</v>
       </c>
-      <c r="C276" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D276" s="54">
+      <c r="C276" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D276" s="74">
         <v>336</v>
       </c>
-      <c r="E276" s="54"/>
+      <c r="E276" s="49" t="s">
+        <v>491</v>
+      </c>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A277" s="54" t="s">
+      <c r="A277" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B277" s="54" t="s">
+      <c r="B277" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="C277" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D277" s="54">
+      <c r="C277" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D277" s="74">
         <v>336</v>
       </c>
-      <c r="E277" s="54"/>
+      <c r="E277" s="49" t="s">
+        <v>492</v>
+      </c>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A278" s="54" t="s">
+      <c r="A278" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B278" s="54" t="s">
+      <c r="B278" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="C278" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D278" s="54">
+      <c r="C278" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D278" s="74">
         <v>336</v>
       </c>
-      <c r="E278" s="54"/>
+      <c r="E278" s="49" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A279" s="54" t="s">
+      <c r="A279" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B279" s="54" t="s">
+      <c r="B279" s="49" t="s">
         <v>212</v>
       </c>
-      <c r="C279" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D279" s="54">
+      <c r="C279" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D279" s="74">
         <v>336</v>
       </c>
-      <c r="E279" s="54"/>
+      <c r="E279" s="49" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A280" s="54" t="s">
+      <c r="A280" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B280" s="54" t="s">
+      <c r="B280" s="49" t="s">
         <v>92</v>
       </c>
-      <c r="C280" s="54" t="s">
-        <v>8</v>
-      </c>
-      <c r="D280" s="54">
+      <c r="C280" s="49" t="s">
+        <v>8</v>
+      </c>
+      <c r="D280" s="74">
         <v>336</v>
       </c>
-      <c r="E280" s="54"/>
+      <c r="E280" s="49" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A281" s="54" t="s">
+      <c r="A281" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="B281" s="54" t="s">
+      <c r="B281" s="49" t="s">
         <v>96</v>
       </c>
-      <c r="C281" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D281" s="54">
+      <c r="C281" s="49" t="s">
+        <v>4</v>
+      </c>
+      <c r="D281" s="74">
         <v>336</v>
       </c>
-      <c r="E281" s="54" t="s">
-        <v>391</v>
+      <c r="E281" s="49" t="s">
+        <v>383</v>
       </c>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.35">
@@ -7167,8 +7944,11 @@
       <c r="C282" t="s">
         <v>19</v>
       </c>
-      <c r="D282">
+      <c r="D282" s="6">
         <v>336</v>
+      </c>
+      <c r="E282" s="64" t="s">
+        <v>490</v>
       </c>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.35">
@@ -7181,8 +7961,11 @@
       <c r="C283" t="s">
         <v>4</v>
       </c>
-      <c r="D283">
+      <c r="D283" s="6">
         <v>336</v>
+      </c>
+      <c r="E283" s="64" t="s">
+        <v>491</v>
       </c>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.35">
@@ -7195,8 +7978,11 @@
       <c r="C284" t="s">
         <v>4</v>
       </c>
-      <c r="D284">
+      <c r="D284" s="6">
         <v>336</v>
+      </c>
+      <c r="E284" s="64" t="s">
+        <v>492</v>
       </c>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.35">
@@ -7209,8 +7995,11 @@
       <c r="C285" t="s">
         <v>4</v>
       </c>
-      <c r="D285">
+      <c r="D285" s="6">
         <v>336</v>
+      </c>
+      <c r="E285" s="64" t="s">
+        <v>493</v>
       </c>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.35">
@@ -7223,8 +8012,11 @@
       <c r="C286" t="s">
         <v>4</v>
       </c>
-      <c r="D286">
+      <c r="D286" s="6">
         <v>336</v>
+      </c>
+      <c r="E286" s="64" t="s">
+        <v>494</v>
       </c>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.35">
@@ -7237,76 +8029,79 @@
       <c r="C287" t="s">
         <v>8</v>
       </c>
-      <c r="D287">
+      <c r="D287" s="6">
         <v>336</v>
       </c>
+      <c r="E287" s="64" t="s">
+        <v>495</v>
+      </c>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A288" s="60" t="s">
+      <c r="A288" t="s">
         <v>213</v>
       </c>
-      <c r="B288" s="60" t="s">
+      <c r="B288" t="s">
         <v>96</v>
       </c>
-      <c r="C288" s="60" t="s">
-        <v>4</v>
-      </c>
-      <c r="D288" s="60">
+      <c r="C288" t="s">
+        <v>4</v>
+      </c>
+      <c r="D288" s="6">
         <v>336</v>
       </c>
-      <c r="E288" s="60" t="s">
+      <c r="E288" s="64" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A289" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="B289" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C289" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D289" s="72">
+        <v>336</v>
+      </c>
+      <c r="E289" s="47" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A290" s="47" t="s">
+        <v>213</v>
+      </c>
+      <c r="B290" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C290" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D290" s="72">
+        <v>336</v>
+      </c>
+      <c r="E290" s="47" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A289" s="55" t="s">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A291" s="47" t="s">
         <v>213</v>
       </c>
-      <c r="B289" s="55" t="s">
-        <v>62</v>
-      </c>
-      <c r="C289" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D289" s="55">
+      <c r="B291" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="C291" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="D291" s="72">
         <v>336</v>
       </c>
-      <c r="E289" s="62" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A290" s="55" t="s">
-        <v>213</v>
-      </c>
-      <c r="B290" s="55" t="s">
-        <v>94</v>
-      </c>
-      <c r="C290" s="55" t="s">
-        <v>4</v>
-      </c>
-      <c r="D290" s="55">
-        <v>336</v>
-      </c>
-      <c r="E290" s="55" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A291" s="62" t="s">
-        <v>213</v>
-      </c>
-      <c r="B291" s="62" t="s">
-        <v>63</v>
-      </c>
-      <c r="C291" s="62" t="s">
-        <v>4</v>
-      </c>
-      <c r="D291" s="62">
-        <v>336</v>
-      </c>
-      <c r="E291" s="62" t="s">
-        <v>393</v>
+      <c r="E291" s="47" t="s">
+        <v>385</v>
       </c>
     </row>
   </sheetData>
@@ -7339,126 +8134,126 @@
       <c r="D1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" s="63" t="s">
-        <v>404</v>
-      </c>
-      <c r="B2" s="54" t="s">
+      <c r="A2" s="54" t="s">
+        <v>396</v>
+      </c>
+      <c r="B2" s="44" t="s">
         <v>217</v>
       </c>
-      <c r="C2" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D2" s="54" t="s">
-        <v>400</v>
+      <c r="C2" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D2" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E2" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" s="64"/>
-      <c r="B3" s="54" t="s">
+      <c r="A3" s="55"/>
+      <c r="B3" s="44" t="s">
         <v>219</v>
       </c>
-      <c r="C3" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D3" s="54" t="s">
-        <v>400</v>
+      <c r="C3" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D3" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E3" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" s="64"/>
-      <c r="B4" s="54" t="s">
+      <c r="A4" s="55"/>
+      <c r="B4" s="44" t="s">
         <v>221</v>
       </c>
-      <c r="C4" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D4" s="54" t="s">
-        <v>400</v>
+      <c r="C4" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" s="64"/>
-      <c r="B5" s="54" t="s">
+      <c r="A5" s="55"/>
+      <c r="B5" s="44" t="s">
         <v>223</v>
       </c>
-      <c r="C5" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" s="54" t="s">
-        <v>400</v>
+      <c r="C5" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E5" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" s="64"/>
-      <c r="B6" s="54" t="s">
+      <c r="A6" s="55"/>
+      <c r="B6" s="44" t="s">
         <v>225</v>
       </c>
-      <c r="C6" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D6" s="54" t="s">
-        <v>400</v>
+      <c r="C6" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D6" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E6" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" s="64"/>
-      <c r="B7" s="54" t="s">
+      <c r="A7" s="55"/>
+      <c r="B7" s="44" t="s">
         <v>227</v>
       </c>
-      <c r="C7" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D7" s="54" t="s">
-        <v>400</v>
+      <c r="C7" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E7" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A8" s="64"/>
-      <c r="B8" s="54" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="44" t="s">
         <v>229</v>
       </c>
-      <c r="C8" s="54" t="s">
-        <v>377</v>
-      </c>
-      <c r="D8" s="54" t="s">
-        <v>400</v>
+      <c r="C8" s="44" t="s">
+        <v>370</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>392</v>
       </c>
       <c r="E8" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A9" s="38" t="s">
-        <v>405</v>
+      <c r="A9" s="56" t="s">
+        <v>397</v>
       </c>
       <c r="B9" t="s">
         <v>252</v>
       </c>
       <c r="C9" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D9" t="s">
         <v>253</v>
@@ -7468,12 +8263,12 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A10" s="38"/>
+      <c r="A10" s="56"/>
       <c r="B10" t="s">
         <v>255</v>
       </c>
       <c r="C10" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D10" t="s">
         <v>256</v>
@@ -7483,12 +8278,12 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A11" s="38"/>
+      <c r="A11" s="56"/>
       <c r="B11" t="s">
         <v>258</v>
       </c>
       <c r="C11" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D11" t="s">
         <v>259</v>
@@ -7498,12 +8293,12 @@
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A12" s="38"/>
+      <c r="A12" s="56"/>
       <c r="B12" t="s">
         <v>261</v>
       </c>
       <c r="C12" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="D12" t="s">
         <v>262</v>
@@ -7513,46 +8308,46 @@
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A13" s="38" t="s">
-        <v>406</v>
-      </c>
-      <c r="B13" s="54" t="s">
+      <c r="A13" s="56" t="s">
+        <v>398</v>
+      </c>
+      <c r="B13" s="44" t="s">
         <v>231</v>
       </c>
-      <c r="C13" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13" s="65" t="s">
-        <v>401</v>
+      <c r="C13" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D13" s="51" t="s">
+        <v>393</v>
       </c>
       <c r="E13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A14" s="38"/>
-      <c r="B14" s="54" t="s">
+      <c r="A14" s="56"/>
+      <c r="B14" s="44" t="s">
         <v>233</v>
       </c>
-      <c r="C14" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D14" s="65" t="s">
-        <v>402</v>
+      <c r="C14" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D14" s="51" t="s">
+        <v>394</v>
       </c>
       <c r="E14" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A15" s="38"/>
-      <c r="B15" s="54" t="s">
+      <c r="A15" s="56"/>
+      <c r="B15" s="44" t="s">
         <v>235</v>
       </c>
-      <c r="C15" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D15" s="54" t="s">
+      <c r="C15" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15" s="44" t="s">
         <v>236</v>
       </c>
       <c r="E15" t="s">
@@ -7560,14 +8355,14 @@
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A16" s="38"/>
-      <c r="B16" s="54" t="s">
+      <c r="A16" s="56"/>
+      <c r="B16" s="44" t="s">
         <v>238</v>
       </c>
-      <c r="C16" s="54" t="s">
-        <v>4</v>
-      </c>
-      <c r="D16" s="54" t="s">
+      <c r="C16" s="44" t="s">
+        <v>4</v>
+      </c>
+      <c r="D16" s="44" t="s">
         <v>239</v>
       </c>
       <c r="E16" t="s">
@@ -7575,14 +8370,14 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="38"/>
-      <c r="B17" s="54" t="s">
+      <c r="A17" s="56"/>
+      <c r="B17" s="44" t="s">
         <v>247</v>
       </c>
-      <c r="C17" s="54" t="s">
-        <v>378</v>
-      </c>
-      <c r="D17" s="54" t="s">
+      <c r="C17" s="44" t="s">
+        <v>371</v>
+      </c>
+      <c r="D17" s="44" t="s">
         <v>248</v>
       </c>
       <c r="E17" t="s">
@@ -7590,31 +8385,31 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="64" t="s">
-        <v>410</v>
-      </c>
-      <c r="B18" s="29" t="s">
+      <c r="A18" s="55" t="s">
+        <v>402</v>
+      </c>
+      <c r="B18" t="s">
         <v>250</v>
       </c>
-      <c r="C18" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D18" s="29" t="s">
+      <c r="C18" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" t="s">
         <v>251</v>
       </c>
       <c r="E18" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="38"/>
-      <c r="B19" s="29" t="s">
+      <c r="A19" s="56"/>
+      <c r="B19" t="s">
         <v>241</v>
       </c>
-      <c r="C19" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="29" t="s">
+      <c r="C19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" t="s">
         <v>242</v>
       </c>
       <c r="E19" t="s">
@@ -7622,14 +8417,14 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="38"/>
-      <c r="B20" s="29" t="s">
+      <c r="A20" s="56"/>
+      <c r="B20" t="s">
         <v>244</v>
       </c>
-      <c r="C20" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20" s="29" t="s">
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
         <v>245</v>
       </c>
       <c r="E20" t="s">
